--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A143F4CB-6750-4D2A-A2C8-5E2EFD249456}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDFAF264-9685-4396-A31B-E92C0590539E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="1" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
   <sheets>
     <sheet name="galinhas" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="100">
   <si>
     <t>HOJE</t>
   </si>
@@ -328,6 +328,9 @@
   </si>
   <si>
     <t>?</t>
+  </si>
+  <si>
+    <t>Filó</t>
   </si>
 </sst>
 </file>
@@ -1110,28 +1113,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B71D903-D903-49BC-88F3-86B94027E03B}">
   <dimension ref="A1:J58"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.453125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.1796875" style="1"/>
-    <col min="3" max="3" width="16.81640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.453125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="14.26953125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="10.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.1796875" style="2"/>
-    <col min="8" max="8" width="11.7265625" style="11" customWidth="1"/>
-    <col min="9" max="9" width="10.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.26953125" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9.1796875" style="2"/>
+    <col min="1" max="1" width="15.42578125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="16.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="2"/>
+    <col min="8" max="8" width="11.7109375" style="11" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="5" customFormat="1" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1147,7 +1150,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="3" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" s="3" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
@@ -1170,7 +1173,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>17</v>
       </c>
@@ -1198,7 +1201,7 @@
         <v>0.76190476190476186</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>17</v>
       </c>
@@ -1226,7 +1229,7 @@
         <v>0.76190476190476186</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>17</v>
       </c>
@@ -1255,7 +1258,7 @@
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>17</v>
       </c>
@@ -1284,7 +1287,7 @@
         <v>0.38095238095238093</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>17</v>
       </c>
@@ -1313,7 +1316,7 @@
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="8" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>18</v>
       </c>
@@ -1341,7 +1344,7 @@
         <v>0.72727272727272729</v>
       </c>
     </row>
-    <row r="9" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>18</v>
       </c>
@@ -1369,7 +1372,7 @@
         <v>0.72727272727272729</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>18</v>
       </c>
@@ -1393,7 +1396,7 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="39" t="s">
         <v>17</v>
       </c>
@@ -1408,18 +1411,18 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>17</v>
       </c>
@@ -1444,7 +1447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>17</v>
       </c>
@@ -1472,7 +1475,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>17</v>
       </c>
@@ -1500,7 +1503,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>18</v>
       </c>
@@ -1515,21 +1518,21 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>3.0769230769230771E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.35">
+        <v>3.0042918454935622E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>18</v>
       </c>
@@ -1556,7 +1559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>18</v>
       </c>
@@ -1583,7 +1586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>17</v>
       </c>
@@ -1611,7 +1614,7 @@
         <v>0.61904761904761907</v>
       </c>
     </row>
-    <row r="19" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
         <v>17</v>
       </c>
@@ -1626,24 +1629,24 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>3.90625E-2</v>
+        <v>3.7974683544303799E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:10" s="24" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="24" t="s">
         <v>17</v>
       </c>
@@ -1671,7 +1674,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="21" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>18</v>
       </c>
@@ -1700,13 +1703,13 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-352</v>
+        <v>-363</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>18</v>
       </c>
@@ -1735,13 +1738,13 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-352</v>
+        <v>-363</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>18</v>
       </c>
@@ -1775,7 +1778,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
         <v>22</v>
       </c>
@@ -1790,24 +1793,24 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>8.3798882681564244E-3</v>
+        <v>8.130081300813009E-3</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
         <v>22</v>
       </c>
@@ -1822,7 +1825,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1838,7 +1841,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
         <v>22</v>
       </c>
@@ -1853,24 +1856,24 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>8.3798882681564244E-3</v>
+        <v>8.130081300813009E-3</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
         <v>22</v>
       </c>
@@ -1885,24 +1888,24 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>8.3798882681564244E-3</v>
+        <v>8.130081300813009E-3</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="28" t="s">
         <v>32</v>
       </c>
@@ -1920,7 +1923,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
         <v>18</v>
       </c>
@@ -1947,7 +1950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
         <v>18</v>
       </c>
@@ -1981,7 +1984,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
         <v>17</v>
       </c>
@@ -2015,7 +2018,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
         <v>17</v>
       </c>
@@ -2049,7 +2052,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:10" s="43" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:10" s="43" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="43" t="s">
         <v>17</v>
       </c>
@@ -2083,7 +2086,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>36</v>
       </c>
@@ -2113,7 +2116,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
         <v>22</v>
       </c>
@@ -2135,7 +2138,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
         <v>32</v>
       </c>
@@ -2153,7 +2156,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="28" t="s">
         <v>32</v>
       </c>
@@ -2171,7 +2174,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="28" t="s">
         <v>32</v>
       </c>
@@ -2189,7 +2192,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="39" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="28" t="s">
         <v>32</v>
       </c>
@@ -2207,7 +2210,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="28" t="s">
         <v>32</v>
       </c>
@@ -2225,7 +2228,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="41" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="28" t="s">
         <v>32</v>
       </c>
@@ -2237,14 +2240,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2257,7 +2260,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="42" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="17" t="s">
         <v>18</v>
       </c>
@@ -2269,14 +2272,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2289,7 +2292,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
         <v>18</v>
       </c>
@@ -2301,14 +2304,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2321,7 +2324,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="17" t="s">
         <v>18</v>
       </c>
@@ -2333,14 +2336,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2353,7 +2356,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
         <v>17</v>
       </c>
@@ -2384,7 +2387,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
         <v>22</v>
       </c>
@@ -2399,18 +2402,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="55">
         <f ca="1">F46*2</f>
-        <v>906</v>
+        <v>928</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2419,7 +2422,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
         <v>22</v>
       </c>
@@ -2434,18 +2437,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="55">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>638</v>
+        <v>660</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2454,7 +2457,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="48" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
         <v>22</v>
       </c>
@@ -2469,18 +2472,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="55">
         <f t="shared" ca="1" si="12"/>
-        <v>602</v>
+        <v>624</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2489,7 +2492,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="49" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
         <v>22</v>
       </c>
@@ -2506,7 +2509,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="50" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="15" t="s">
         <v>17</v>
       </c>
@@ -2540,7 +2543,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="51" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="17" t="s">
         <v>18</v>
       </c>
@@ -2552,14 +2555,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2572,11 +2575,11 @@
         <v>29</v>
       </c>
     </row>
-    <row r="52" spans="1:10" s="35" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B52" s="36"/>
       <c r="H52" s="27"/>
     </row>
-    <row r="53" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="30" t="s">
         <v>35</v>
       </c>
@@ -2595,7 +2598,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="54" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="30" t="s">
         <v>41</v>
       </c>
@@ -2614,7 +2617,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="55" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="30" t="s">
         <v>79</v>
       </c>
@@ -2632,7 +2635,7 @@
       </c>
       <c r="H55" s="32"/>
     </row>
-    <row r="56" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="30" t="s">
         <v>35</v>
       </c>
@@ -2650,7 +2653,7 @@
       </c>
       <c r="H56" s="32"/>
     </row>
-    <row r="57" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="30" t="s">
         <v>79</v>
       </c>
@@ -2669,7 +2672,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="58" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="30" t="s">
         <v>79</v>
       </c>
@@ -2697,27 +2700,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B0995D-FE85-4EC0-91CA-7B21E8F79AC2}">
   <dimension ref="A1:M23"/>
-  <sheetFormatPr defaultColWidth="10.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="10.7265625" style="47"/>
-    <col min="4" max="4" width="17.453125" style="47" customWidth="1"/>
-    <col min="5" max="5" width="10.7265625" style="47"/>
-    <col min="6" max="6" width="10.7265625" style="48"/>
-    <col min="7" max="7" width="14.7265625" style="48" customWidth="1"/>
-    <col min="8" max="8" width="10.7265625" style="47"/>
-    <col min="9" max="9" width="15.1796875" style="47" customWidth="1"/>
-    <col min="10" max="10" width="13.81640625" style="47" customWidth="1"/>
-    <col min="11" max="16384" width="10.7265625" style="47"/>
+    <col min="1" max="3" width="10.7109375" style="47"/>
+    <col min="4" max="4" width="17.42578125" style="47" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" style="47"/>
+    <col min="6" max="6" width="10.7109375" style="48"/>
+    <col min="7" max="7" width="14.7109375" style="48" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" style="47"/>
+    <col min="9" max="9" width="15.140625" style="47" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" style="47" customWidth="1"/>
+    <col min="11" max="16384" width="10.7109375" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="49" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" s="49" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B1" s="46" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="46"/>
       <c r="D1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="F1" s="46"/>
       <c r="G1" s="46"/>
@@ -2731,7 +2734,7 @@
       <c r="J1" s="58"/>
       <c r="K1" s="58"/>
     </row>
-    <row r="2" spans="1:13" s="50" customFormat="1" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:13" s="50" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="50" t="s">
         <v>59</v>
       </c>
@@ -2767,7 +2770,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="67" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="67" t="s">
         <v>18</v>
       </c>
@@ -2785,14 +2788,14 @@
       </c>
       <c r="F3" s="68">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="G3" s="68">
         <v>45947</v>
       </c>
       <c r="H3" s="67">
         <f t="shared" ref="H3:H8" ca="1" si="0">F3-G3</f>
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="I3" s="67" t="s">
         <v>54</v>
@@ -2808,7 +2811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="67" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="67" t="s">
         <v>18</v>
       </c>
@@ -2826,14 +2829,14 @@
       </c>
       <c r="F4" s="68">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="G4" s="68">
         <v>45953</v>
       </c>
       <c r="H4" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="I4" s="67" t="s">
         <v>54</v>
@@ -2849,7 +2852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="67" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="67" t="s">
         <v>18</v>
       </c>
@@ -2867,14 +2870,14 @@
       </c>
       <c r="F5" s="68">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="G5" s="68">
         <v>45956</v>
       </c>
       <c r="H5" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="I5" s="67" t="s">
         <v>54</v>
@@ -2891,7 +2894,7 @@
       </c>
       <c r="M5" s="74"/>
     </row>
-    <row r="6" spans="1:13" s="70" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" s="70" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="70" t="s">
         <v>18</v>
       </c>
@@ -2909,14 +2912,14 @@
       </c>
       <c r="F6" s="71">
         <f t="shared" ref="F6:F14" ca="1" si="2">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="G6" s="71">
         <v>45910</v>
       </c>
       <c r="H6" s="70">
         <f t="shared" ca="1" si="0"/>
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="I6" s="70" t="s">
         <v>54</v>
@@ -2933,7 +2936,7 @@
       </c>
       <c r="M6" s="67"/>
     </row>
-    <row r="7" spans="1:13" s="67" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="67" t="s">
         <v>18</v>
       </c>
@@ -2951,14 +2954,14 @@
       </c>
       <c r="F7" s="68">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="G7" s="68">
         <v>46027</v>
       </c>
       <c r="H7" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="I7" s="67" t="s">
         <v>54</v>
@@ -2974,7 +2977,7 @@
         <v>0.14285714285714285</v>
       </c>
     </row>
-    <row r="8" spans="1:13" s="74" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" s="74" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="74" t="s">
         <v>18</v>
       </c>
@@ -2992,14 +2995,14 @@
       </c>
       <c r="F8" s="75">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="G8" s="75">
         <v>46036</v>
       </c>
       <c r="H8" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="I8" s="74" t="s">
         <v>54</v>
@@ -3015,48 +3018,48 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="17" t="s">
+    <row r="9" spans="1:13" s="74" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="74" t="s">
         <v>80</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="74" t="s">
         <v>81</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="75">
         <f t="shared" ca="1" si="2"/>
-        <v>46262</v>
-      </c>
-      <c r="G9" s="18">
+        <v>46273</v>
+      </c>
+      <c r="G9" s="75">
         <v>46082</v>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="74">
         <f ca="1">F9-G9</f>
-        <v>180</v>
-      </c>
-      <c r="I9" s="17" t="s">
+        <v>191</v>
+      </c>
+      <c r="I9" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="17">
+      <c r="J9" s="74">
         <v>10</v>
       </c>
-      <c r="K9" s="17">
+      <c r="K9" s="74">
         <v>4</v>
       </c>
-      <c r="L9" s="22">
+      <c r="L9" s="78">
         <f t="shared" si="1"/>
         <v>0.4</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>18</v>
       </c>
@@ -3074,14 +3077,14 @@
       </c>
       <c r="F10" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="G10" s="18">
         <v>46089</v>
       </c>
       <c r="H10" s="17">
-        <f t="shared" ref="H10:H12" ca="1" si="3">F10-G10</f>
-        <v>173</v>
+        <f t="shared" ref="H10:H17" ca="1" si="3">F10-G10</f>
+        <v>184</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>54</v>
@@ -3097,7 +3100,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="72" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" s="72" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="72" t="s">
         <v>17</v>
       </c>
@@ -3115,14 +3118,14 @@
       </c>
       <c r="F11" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="G11" s="73">
         <v>46129</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I11" s="17" t="s">
         <v>54</v>
@@ -3138,7 +3141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:13" s="72" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" s="72" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C12" s="72" t="s">
         <v>84</v>
       </c>
@@ -3150,14 +3153,14 @@
       </c>
       <c r="F12" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="G12" s="73">
         <v>46129</v>
       </c>
       <c r="H12" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>54</v>
@@ -3166,85 +3169,84 @@
         <v>3</v>
       </c>
       <c r="K12" s="72">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L12" s="22">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" s="72" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C13" s="72" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" s="74" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="74" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="72" t="s">
+      <c r="D13" s="74" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="72" t="s">
+      <c r="E13" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="75">
         <f t="shared" ca="1" si="2"/>
-        <v>46262</v>
-      </c>
-      <c r="G13" s="73">
+        <v>46273</v>
+      </c>
+      <c r="G13" s="75">
         <v>46182</v>
       </c>
-      <c r="H13" s="17">
-        <f ca="1">G13-F13</f>
-        <v>-80</v>
-      </c>
-      <c r="I13" s="72" t="s">
+      <c r="H13" s="74">
+        <f t="shared" ca="1" si="3"/>
+        <v>91</v>
+      </c>
+      <c r="I13" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="J13" s="72">
+      <c r="J13" s="74">
         <v>4</v>
       </c>
-      <c r="K13" s="72">
+      <c r="K13" s="74">
         <v>3</v>
       </c>
-      <c r="L13" s="22">
+      <c r="L13" s="78">
         <f t="shared" si="1"/>
         <v>0.75</v>
       </c>
     </row>
-    <row r="14" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C14" s="76" t="s">
+    <row r="14" spans="1:13" s="74" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="74" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="76" t="s">
+      <c r="D14" s="74" t="s">
         <v>91</v>
       </c>
-      <c r="E14" s="76" t="s">
+      <c r="E14" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="75">
         <f t="shared" ca="1" si="2"/>
-        <v>46262</v>
-      </c>
-      <c r="G14" s="77">
+        <v>46273</v>
+      </c>
+      <c r="G14" s="75">
         <v>46184</v>
       </c>
-      <c r="H14" s="17">
-        <f ca="1">G14-F14</f>
-        <v>-78</v>
-      </c>
-      <c r="I14" s="72" t="s">
+      <c r="H14" s="74">
+        <f t="shared" ca="1" si="3"/>
+        <v>89</v>
+      </c>
+      <c r="I14" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="J14" s="72">
+      <c r="J14" s="74">
         <v>1</v>
       </c>
-      <c r="K14" s="72">
+      <c r="K14" s="74">
         <v>1</v>
       </c>
-      <c r="L14" s="22">
+      <c r="L14" s="78">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="M14" s="17"/>
-    </row>
-    <row r="15" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C15" s="17" t="s">
         <v>95</v>
       </c>
@@ -3256,14 +3258,14 @@
       </c>
       <c r="F15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="G15" s="18">
         <v>46216</v>
       </c>
       <c r="H15" s="17">
-        <f ca="1">F15-G15</f>
-        <v>46</v>
+        <f t="shared" ca="1" si="3"/>
+        <v>57</v>
       </c>
       <c r="I15" s="72" t="s">
         <v>54</v>
@@ -3279,51 +3281,78 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="C16" s="17" t="s">
+    <row r="16" spans="1:13" s="74" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="74" t="s">
         <v>97</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="75">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
-      </c>
-      <c r="G16" s="18">
+        <v>46273</v>
+      </c>
+      <c r="G16" s="75">
         <f t="shared" ref="G16" ca="1" si="4">TODAY()</f>
-        <v>46262</v>
-      </c>
-      <c r="H16" s="17">
-        <f t="shared" ref="H16" ca="1" si="5">G16-F16</f>
+        <v>46273</v>
+      </c>
+      <c r="H16" s="74">
+        <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="I16" s="72" t="s">
+      <c r="I16" s="74" t="s">
         <v>54</v>
       </c>
-      <c r="J16" s="72">
+      <c r="J16" s="74">
         <v>6</v>
       </c>
-      <c r="K16" s="72">
+      <c r="K16" s="74">
         <v>6</v>
       </c>
-      <c r="L16" s="22">
+      <c r="L16" s="78">
         <f>K16/J16</f>
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="I17" s="72"/>
-      <c r="J17" s="72"/>
-      <c r="K17" s="72"/>
-      <c r="L17" s="22"/>
-    </row>
-    <row r="18" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="18">
+        <f ca="1">TODAY()</f>
+        <v>46273</v>
+      </c>
+      <c r="G17" s="18">
+        <v>46271</v>
+      </c>
+      <c r="H17" s="17">
+        <f t="shared" ca="1" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="I17" s="72" t="s">
+        <v>54</v>
+      </c>
+      <c r="J17" s="72">
+        <v>6</v>
+      </c>
+      <c r="K17" s="72">
+        <v>6</v>
+      </c>
+      <c r="L17" s="22">
+        <f>K17/J17</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
       <c r="I18" s="72"/>
@@ -3331,7 +3360,7 @@
       <c r="K18" s="72"/>
       <c r="L18" s="22"/>
     </row>
-    <row r="19" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C19" s="76"/>
       <c r="D19" s="76"/>
       <c r="E19" s="76"/>
@@ -3344,7 +3373,7 @@
       <c r="L19" s="22"/>
       <c r="M19" s="17"/>
     </row>
-    <row r="20" spans="1:13" s="30" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="30" t="s">
         <v>35</v>
       </c>
@@ -3362,7 +3391,7 @@
       </c>
       <c r="I20" s="32"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G23" s="18"/>
       <c r="H23" s="17"/>
       <c r="I23" s="17"/>
@@ -3379,28 +3408,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21D6C99-536E-4F31-8A16-5ECA51AF8689}">
   <dimension ref="A1:K28"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.26953125" style="47" customWidth="1"/>
-    <col min="2" max="2" width="9.1796875" style="47"/>
-    <col min="3" max="3" width="19.453125" style="47" customWidth="1"/>
-    <col min="4" max="4" width="14.26953125" style="47" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" style="47" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="47"/>
+    <col min="3" max="3" width="19.42578125" style="47" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" style="47" customWidth="1"/>
     <col min="5" max="5" width="13" style="48" customWidth="1"/>
-    <col min="6" max="6" width="16.81640625" style="48" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" style="48" customWidth="1"/>
     <col min="7" max="7" width="13" style="47" customWidth="1"/>
-    <col min="8" max="8" width="15.1796875" style="47" customWidth="1"/>
-    <col min="9" max="9" width="15.26953125" style="47" customWidth="1"/>
-    <col min="10" max="10" width="11.7265625" style="47" customWidth="1"/>
-    <col min="11" max="16384" width="9.1796875" style="47"/>
+    <col min="8" max="8" width="15.140625" style="47" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" style="47" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" style="47" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="49" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" s="49" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B1" s="46" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3412,7 +3441,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="56" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" s="56" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
         <v>59</v>
       </c>
@@ -3444,7 +3473,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="59" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" s="59" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="59" t="s">
         <v>17</v>
       </c>
@@ -3478,7 +3507,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="59" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" s="59" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="59" t="s">
         <v>17</v>
       </c>
@@ -3509,7 +3538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="62" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" s="62" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="59" t="s">
         <v>17</v>
       </c>
@@ -3540,7 +3569,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="62" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" s="62" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="62" t="s">
         <v>17</v>
       </c>
@@ -3574,11 +3603,11 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="65" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" s="65" customFormat="1" x14ac:dyDescent="0.25">
       <c r="E7" s="66"/>
       <c r="F7" s="66"/>
     </row>
-    <row r="9" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="67" t="s">
         <v>17</v>
       </c>
@@ -3612,7 +3641,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="67" t="s">
         <v>17</v>
       </c>
@@ -3646,7 +3675,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="67" t="s">
         <v>17</v>
       </c>
@@ -3680,7 +3709,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>17</v>
       </c>
@@ -3714,12 +3743,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="E13" s="16"/>
       <c r="F13" s="16"/>
       <c r="I13" s="33"/>
     </row>
-    <row r="14" spans="1:10" s="80" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" s="80" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="80" t="s">
         <v>88</v>
       </c>
@@ -3750,7 +3779,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="80" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" s="80" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="80" t="s">
         <v>90</v>
       </c>
@@ -3777,7 +3806,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="80" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" s="80" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="80" t="s">
         <v>90</v>
       </c>
@@ -3808,7 +3837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11" s="76" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" s="76" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C17" s="80" t="s">
         <v>8</v>
       </c>
@@ -3837,7 +3866,7 @@
       </c>
       <c r="K17" s="80"/>
     </row>
-    <row r="18" spans="1:11" s="80" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" s="80" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="80" t="s">
         <v>18</v>
       </c>
@@ -3871,7 +3900,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:11" s="80" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" s="80" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="80" t="s">
         <v>18</v>
       </c>
@@ -3879,7 +3908,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:11" s="80" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" s="80" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="80" t="s">
         <v>6</v>
       </c>
@@ -3910,7 +3939,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:11" s="80" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" s="80" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="80" t="s">
         <v>9</v>
       </c>
@@ -3941,7 +3970,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="84" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" s="84" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="17" t="s">
         <v>84</v>
       </c>
@@ -3955,8 +3984,8 @@
         <v>98</v>
       </c>
       <c r="F22" s="18">
-        <f t="shared" ref="F22:F23" ca="1" si="0">TODAY()</f>
-        <v>46262</v>
+        <f t="shared" ref="F22" ca="1" si="0">TODAY()</f>
+        <v>46273</v>
       </c>
       <c r="G22" s="17" t="e">
         <f t="shared" ref="G22:G23" ca="1" si="1">F22-E22</f>
@@ -3970,7 +3999,7 @@
       <c r="J22" s="17"/>
       <c r="K22" s="22"/>
     </row>
-    <row r="23" spans="1:11" s="80" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" s="80" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="80" t="s">
         <v>96</v>
       </c>
@@ -4001,7 +4030,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B24" s="72"/>
       <c r="C24" s="72"/>
       <c r="D24" s="72"/>
@@ -4013,7 +4042,7 @@
       <c r="J24" s="72"/>
       <c r="K24" s="22"/>
     </row>
-    <row r="25" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="30" t="s">
         <v>79</v>
       </c>
@@ -4032,7 +4061,7 @@
       <c r="F25" s="31"/>
       <c r="I25" s="32"/>
     </row>
-    <row r="27" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="59"/>
       <c r="B27" s="62" t="s">
         <v>80</v>
@@ -4064,7 +4093,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="62" t="s">
         <v>7</v>
       </c>
@@ -4104,21 +4133,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC1ACAAB-4C7C-47DD-B348-5E0B06D77598}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.26953125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1796875" style="1"/>
-    <col min="3" max="3" width="16.453125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7265625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.26953125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.54296875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.1796875" style="1"/>
-    <col min="8" max="8" width="9.1796875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.453125" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.1796875" style="1"/>
+    <col min="1" max="1" width="13.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="16.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="1"/>
+    <col min="8" max="8" width="9.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>59</v>
       </c>
@@ -4148,7 +4177,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>22</v>
       </c>
@@ -4163,11 +4192,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -4180,7 +4209,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>22</v>
       </c>
@@ -4195,11 +4224,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46273</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>
@@ -4212,7 +4241,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="30" t="s">
         <v>79</v>
       </c>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDFAF264-9685-4396-A31B-E92C0590539E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155279F8-4E6C-49D3-9358-553CC24EBD9E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="1" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
   <sheets>
     <sheet name="galinhas" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="100">
   <si>
     <t>HOJE</t>
   </si>
@@ -544,7 +544,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -702,9 +702,6 @@
     <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -738,12 +735,6 @@
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -784,19 +775,19 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1134,7 +1125,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46291</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1143,10 +1134,10 @@
       <c r="E1" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="54" t="s">
+      <c r="G1" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="H1" s="55">
+      <c r="H1" s="54">
         <v>2</v>
       </c>
     </row>
@@ -1411,11 +1402,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46291</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1518,18 +1509,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46291</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>3.0042918454935622E-2</v>
+        <v>2.8925619834710745E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
@@ -1629,18 +1620,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46291</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>3.7974683544303799E-2</v>
+        <v>3.6319612590799029E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1703,7 +1694,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-363</v>
+        <v>-381</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1738,7 +1729,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-363</v>
+        <v>-381</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1793,18 +1784,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46291</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>8.130081300813009E-3</v>
+        <v>7.7519379844961239E-3</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1825,7 +1816,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46291</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1856,18 +1847,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46291</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>8.130081300813009E-3</v>
+        <v>7.7519379844961239E-3</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1888,18 +1879,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46291</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>8.130081300813009E-3</v>
+        <v>7.7519379844961239E-3</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2240,14 +2231,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46291</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2272,14 +2263,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46291</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2304,14 +2295,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46291</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2336,14 +2327,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46291</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2402,18 +2393,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46291</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="H46" s="55">
+      <c r="H46" s="54">
         <f ca="1">F46*2</f>
-        <v>928</v>
+        <v>964</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2437,18 +2428,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46273</v>
+        <v>46291</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="H47" s="55">
+      <c r="H47" s="54">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>660</v>
+        <v>696</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2472,18 +2463,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46273</v>
+        <v>46291</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="H48" s="55">
+      <c r="H48" s="54">
         <f t="shared" ca="1" si="12"/>
-        <v>624</v>
+        <v>660</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2504,7 +2495,7 @@
       </c>
       <c r="D49" s="20"/>
       <c r="E49" s="20"/>
-      <c r="H49" s="55"/>
+      <c r="H49" s="54"/>
       <c r="J49" s="19" t="s">
         <v>29</v>
       </c>
@@ -2555,14 +2546,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46291</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2720,7 +2711,7 @@
       <c r="C1" s="46"/>
       <c r="D1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46291</v>
       </c>
       <c r="F1" s="46"/>
       <c r="G1" s="46"/>
@@ -2731,8 +2722,8 @@
       <c r="I1" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
     </row>
     <row r="2" spans="1:13" s="50" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="50" t="s">
@@ -2766,295 +2757,295 @@
       <c r="K2" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="L2" s="79" t="s">
+      <c r="L2" s="76" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="67" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="67" t="s">
+    <row r="3" spans="1:13" s="64" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="67" t="s">
+      <c r="D3" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="67" t="s">
+      <c r="E3" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="68">
+      <c r="F3" s="65">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
-      </c>
-      <c r="G3" s="68">
+        <v>46291</v>
+      </c>
+      <c r="G3" s="65">
         <v>45947</v>
       </c>
-      <c r="H3" s="67">
+      <c r="H3" s="64">
         <f t="shared" ref="H3:H8" ca="1" si="0">F3-G3</f>
-        <v>326</v>
-      </c>
-      <c r="I3" s="67" t="s">
+        <v>344</v>
+      </c>
+      <c r="I3" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="J3" s="67">
+      <c r="J3" s="64">
         <v>4</v>
       </c>
-      <c r="K3" s="67">
+      <c r="K3" s="64">
         <v>0</v>
       </c>
-      <c r="L3" s="69">
+      <c r="L3" s="66">
         <f>K3/J3</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="67" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="67" t="s">
+    <row r="4" spans="1:13" s="64" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="67" t="s">
+      <c r="B4" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="67" t="s">
+      <c r="C4" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="67" t="s">
+      <c r="D4" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="67" t="s">
+      <c r="E4" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="68">
+      <c r="F4" s="65">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
-      </c>
-      <c r="G4" s="68">
+        <v>46291</v>
+      </c>
+      <c r="G4" s="65">
         <v>45953</v>
       </c>
-      <c r="H4" s="67">
+      <c r="H4" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>320</v>
-      </c>
-      <c r="I4" s="67" t="s">
+        <v>338</v>
+      </c>
+      <c r="I4" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="J4" s="67">
+      <c r="J4" s="64">
         <v>8</v>
       </c>
-      <c r="K4" s="67">
+      <c r="K4" s="64">
         <v>0</v>
       </c>
-      <c r="L4" s="69">
+      <c r="L4" s="66">
         <f t="shared" ref="L4:L14" si="1">K4/J4</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="67" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="67" t="s">
+    <row r="5" spans="1:13" s="64" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="67" t="s">
+      <c r="B5" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="67" t="s">
+      <c r="C5" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="67" t="s">
+      <c r="D5" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="67" t="s">
+      <c r="E5" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="68">
+      <c r="F5" s="65">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
-      </c>
-      <c r="G5" s="68">
+        <v>46291</v>
+      </c>
+      <c r="G5" s="65">
         <v>45956</v>
       </c>
-      <c r="H5" s="67">
+      <c r="H5" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>317</v>
-      </c>
-      <c r="I5" s="67" t="s">
+        <v>335</v>
+      </c>
+      <c r="I5" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="J5" s="67">
+      <c r="J5" s="64">
         <v>8</v>
       </c>
-      <c r="K5" s="74">
+      <c r="K5" s="71">
         <v>4</v>
       </c>
-      <c r="L5" s="78">
+      <c r="L5" s="75">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="M5" s="74"/>
-    </row>
-    <row r="6" spans="1:13" s="70" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="70" t="s">
+      <c r="M5" s="71"/>
+    </row>
+    <row r="6" spans="1:13" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="70" t="s">
+      <c r="B6" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="70" t="s">
+      <c r="C6" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="70" t="s">
+      <c r="E6" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="71">
+      <c r="F6" s="68">
         <f t="shared" ref="F6:F14" ca="1" si="2">TODAY()</f>
-        <v>46273</v>
-      </c>
-      <c r="G6" s="71">
+        <v>46291</v>
+      </c>
+      <c r="G6" s="68">
         <v>45910</v>
       </c>
-      <c r="H6" s="70">
+      <c r="H6" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>363</v>
-      </c>
-      <c r="I6" s="70" t="s">
+        <v>381</v>
+      </c>
+      <c r="I6" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="J6" s="70">
+      <c r="J6" s="67">
         <v>6</v>
       </c>
-      <c r="K6" s="67">
+      <c r="K6" s="64">
         <v>1</v>
       </c>
-      <c r="L6" s="69">
+      <c r="L6" s="66">
         <f t="shared" si="1"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="M6" s="67"/>
-    </row>
-    <row r="7" spans="1:13" s="67" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="67" t="s">
+      <c r="M6" s="64"/>
+    </row>
+    <row r="7" spans="1:13" s="64" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="67" t="s">
+      <c r="B7" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="67" t="s">
+      <c r="C7" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="67" t="s">
+      <c r="D7" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="67" t="s">
+      <c r="E7" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="68">
+      <c r="F7" s="65">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
-      </c>
-      <c r="G7" s="68">
+        <v>46291</v>
+      </c>
+      <c r="G7" s="65">
         <v>46027</v>
       </c>
-      <c r="H7" s="67">
+      <c r="H7" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>246</v>
-      </c>
-      <c r="I7" s="67" t="s">
+        <v>264</v>
+      </c>
+      <c r="I7" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="J7" s="67">
+      <c r="J7" s="64">
         <v>7</v>
       </c>
-      <c r="K7" s="67">
+      <c r="K7" s="64">
         <v>1</v>
       </c>
-      <c r="L7" s="69">
+      <c r="L7" s="66">
         <f t="shared" si="1"/>
         <v>0.14285714285714285</v>
       </c>
     </row>
-    <row r="8" spans="1:13" s="74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="74" t="s">
+    <row r="8" spans="1:13" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="74" t="s">
+      <c r="B8" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="74" t="s">
+      <c r="C8" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="74" t="s">
+      <c r="D8" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="74" t="s">
+      <c r="E8" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="75">
+      <c r="F8" s="72">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
-      </c>
-      <c r="G8" s="75">
+        <v>46291</v>
+      </c>
+      <c r="G8" s="72">
         <v>46036</v>
       </c>
-      <c r="H8" s="74">
+      <c r="H8" s="71">
         <f t="shared" ca="1" si="0"/>
-        <v>237</v>
-      </c>
-      <c r="I8" s="74" t="s">
+        <v>255</v>
+      </c>
+      <c r="I8" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="J8" s="74">
+      <c r="J8" s="71">
         <v>9</v>
       </c>
-      <c r="K8" s="74">
+      <c r="K8" s="71">
         <v>3</v>
       </c>
-      <c r="L8" s="78">
+      <c r="L8" s="75">
         <f t="shared" si="1"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="74" t="s">
+    <row r="9" spans="1:13" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="71" t="s">
         <v>80</v>
       </c>
-      <c r="C9" s="74" t="s">
+      <c r="C9" s="71" t="s">
         <v>80</v>
       </c>
-      <c r="D9" s="74" t="s">
+      <c r="D9" s="71" t="s">
         <v>81</v>
       </c>
-      <c r="E9" s="74" t="s">
+      <c r="E9" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="75">
+      <c r="F9" s="72">
         <f t="shared" ca="1" si="2"/>
-        <v>46273</v>
-      </c>
-      <c r="G9" s="75">
+        <v>46291</v>
+      </c>
+      <c r="G9" s="72">
         <v>46082</v>
       </c>
-      <c r="H9" s="74">
+      <c r="H9" s="71">
         <f ca="1">F9-G9</f>
-        <v>191</v>
-      </c>
-      <c r="I9" s="74" t="s">
+        <v>209</v>
+      </c>
+      <c r="I9" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="74">
+      <c r="J9" s="71">
         <v>10</v>
       </c>
-      <c r="K9" s="74">
+      <c r="K9" s="71">
         <v>4</v>
       </c>
-      <c r="L9" s="78">
+      <c r="L9" s="75">
         <f t="shared" si="1"/>
         <v>0.4</v>
       </c>
@@ -3077,14 +3068,14 @@
       </c>
       <c r="F10" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46273</v>
+        <v>46291</v>
       </c>
       <c r="G10" s="18">
         <v>46089</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" ref="H10:H17" ca="1" si="3">F10-G10</f>
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>54</v>
@@ -3100,40 +3091,40 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="72" t="s">
+    <row r="11" spans="1:13" s="69" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="69" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="72" t="s">
+      <c r="B11" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="72" t="s">
+      <c r="C11" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="72" t="s">
+      <c r="D11" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="72" t="s">
+      <c r="E11" s="69" t="s">
         <v>29</v>
       </c>
       <c r="F11" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46273</v>
-      </c>
-      <c r="G11" s="73">
+        <v>46291</v>
+      </c>
+      <c r="G11" s="70">
         <v>46129</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="I11" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="J11" s="72">
+      <c r="J11" s="69">
         <v>8</v>
       </c>
-      <c r="K11" s="72">
+      <c r="K11" s="69">
         <v>8</v>
       </c>
       <c r="L11" s="22">
@@ -3141,34 +3132,34 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:13" s="72" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="72" t="s">
+    <row r="12" spans="1:13" s="69" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="D12" s="72" t="s">
+      <c r="D12" s="69" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="72" t="s">
+      <c r="E12" s="69" t="s">
         <v>34</v>
       </c>
       <c r="F12" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46273</v>
-      </c>
-      <c r="G12" s="73">
+        <v>46291</v>
+      </c>
+      <c r="G12" s="70">
         <v>46129</v>
       </c>
       <c r="H12" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="J12" s="72">
+      <c r="J12" s="69">
         <v>3</v>
       </c>
-      <c r="K12" s="72">
+      <c r="K12" s="69">
         <v>0</v>
       </c>
       <c r="L12" s="22">
@@ -3176,72 +3167,72 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" s="74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="74" t="s">
+    <row r="13" spans="1:13" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="71" t="s">
         <v>88</v>
       </c>
-      <c r="D13" s="74" t="s">
+      <c r="D13" s="71" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="74" t="s">
+      <c r="E13" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="75">
+      <c r="F13" s="72">
         <f t="shared" ca="1" si="2"/>
-        <v>46273</v>
-      </c>
-      <c r="G13" s="75">
+        <v>46291</v>
+      </c>
+      <c r="G13" s="72">
         <v>46182</v>
       </c>
-      <c r="H13" s="74">
+      <c r="H13" s="71">
         <f t="shared" ca="1" si="3"/>
-        <v>91</v>
-      </c>
-      <c r="I13" s="74" t="s">
+        <v>109</v>
+      </c>
+      <c r="I13" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="J13" s="74">
+      <c r="J13" s="71">
         <v>4</v>
       </c>
-      <c r="K13" s="74">
+      <c r="K13" s="71">
         <v>3</v>
       </c>
-      <c r="L13" s="78">
+      <c r="L13" s="75">
         <f t="shared" si="1"/>
         <v>0.75</v>
       </c>
     </row>
-    <row r="14" spans="1:13" s="74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="74" t="s">
+    <row r="14" spans="1:13" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="71" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="74" t="s">
+      <c r="D14" s="71" t="s">
         <v>91</v>
       </c>
-      <c r="E14" s="74" t="s">
+      <c r="E14" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="75">
+      <c r="F14" s="72">
         <f t="shared" ca="1" si="2"/>
-        <v>46273</v>
-      </c>
-      <c r="G14" s="75">
+        <v>46291</v>
+      </c>
+      <c r="G14" s="72">
         <v>46184</v>
       </c>
-      <c r="H14" s="74">
+      <c r="H14" s="71">
         <f t="shared" ca="1" si="3"/>
-        <v>89</v>
-      </c>
-      <c r="I14" s="74" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="J14" s="74">
+      <c r="J14" s="71">
         <v>1</v>
       </c>
-      <c r="K14" s="74">
+      <c r="K14" s="71">
         <v>1</v>
       </c>
-      <c r="L14" s="78">
+      <c r="L14" s="75">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -3258,22 +3249,22 @@
       </c>
       <c r="F15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46291</v>
       </c>
       <c r="G15" s="18">
         <v>46216</v>
       </c>
       <c r="H15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>57</v>
-      </c>
-      <c r="I15" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="I15" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="J15" s="72">
+      <c r="J15" s="69">
         <v>8</v>
       </c>
-      <c r="K15" s="72">
+      <c r="K15" s="69">
         <v>8</v>
       </c>
       <c r="L15" s="22">
@@ -3281,38 +3272,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:13" s="74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="74" t="s">
+    <row r="16" spans="1:13" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="71" t="s">
         <v>96</v>
       </c>
-      <c r="D16" s="74" t="s">
+      <c r="D16" s="71" t="s">
         <v>97</v>
       </c>
-      <c r="E16" s="74" t="s">
+      <c r="E16" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="75">
+      <c r="F16" s="72">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
-      </c>
-      <c r="G16" s="75">
+        <v>46291</v>
+      </c>
+      <c r="G16" s="72">
         <f t="shared" ref="G16" ca="1" si="4">TODAY()</f>
-        <v>46273</v>
-      </c>
-      <c r="H16" s="74">
+        <v>46291</v>
+      </c>
+      <c r="H16" s="71">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="I16" s="74" t="s">
+      <c r="I16" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="J16" s="74">
+      <c r="J16" s="71">
         <v>6</v>
       </c>
-      <c r="K16" s="74">
+      <c r="K16" s="71">
         <v>6</v>
       </c>
-      <c r="L16" s="78">
+      <c r="L16" s="75">
         <f>K16/J16</f>
         <v>1</v>
       </c>
@@ -3329,22 +3320,22 @@
       </c>
       <c r="F17" s="18">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46291</v>
       </c>
       <c r="G17" s="18">
         <v>46271</v>
       </c>
       <c r="H17" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>2</v>
-      </c>
-      <c r="I17" s="72" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="J17" s="72">
+      <c r="J17" s="69">
         <v>6</v>
       </c>
-      <c r="K17" s="72">
+      <c r="K17" s="69">
         <v>6</v>
       </c>
       <c r="L17" s="22">
@@ -3355,21 +3346,21 @@
     <row r="18" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="I18" s="72"/>
-      <c r="J18" s="72"/>
-      <c r="K18" s="72"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="69"/>
+      <c r="K18" s="69"/>
       <c r="L18" s="22"/>
     </row>
     <row r="19" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="76"/>
-      <c r="D19" s="76"/>
-      <c r="E19" s="76"/>
+      <c r="C19" s="73"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="73"/>
       <c r="F19" s="18"/>
-      <c r="G19" s="77"/>
+      <c r="G19" s="74"/>
       <c r="H19" s="17"/>
-      <c r="I19" s="72"/>
-      <c r="J19" s="72"/>
-      <c r="K19" s="72"/>
+      <c r="I19" s="69"/>
+      <c r="J19" s="69"/>
+      <c r="K19" s="69"/>
       <c r="L19" s="22"/>
       <c r="M19" s="17"/>
     </row>
@@ -3407,20 +3398,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21D6C99-536E-4F31-8A16-5ECA51AF8689}">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" style="47" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="47"/>
-    <col min="3" max="3" width="19.42578125" style="47" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="47" customWidth="1"/>
-    <col min="5" max="5" width="13" style="48" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" style="48" customWidth="1"/>
-    <col min="7" max="7" width="13" style="47" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" style="47" customWidth="1"/>
-    <col min="9" max="9" width="15.28515625" style="47" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" style="47" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="47"/>
+    <col min="1" max="1" width="13.28515625" style="21" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="21"/>
+    <col min="3" max="3" width="19.42578125" style="21" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="13" style="81" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" style="81" customWidth="1"/>
+    <col min="7" max="7" width="13" style="21" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="21" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" style="21" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" style="21" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="49" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
@@ -3429,7 +3420,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46291</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3437,275 +3428,275 @@
         <f>AVERAGE(I:I)</f>
         <v>#REF!</v>
       </c>
-      <c r="H1" s="53" t="s">
+      <c r="H1" s="49" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="56" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="56" t="s">
+    <row r="2" spans="1:10" s="55" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="56" t="s">
+      <c r="D2" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="56" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="56" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="56" t="s">
+      <c r="G2" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="56" t="s">
+      <c r="H2" s="55" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="56" t="s">
+      <c r="I2" s="55" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="56" t="s">
+      <c r="J2" s="55" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="59" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
+    <row r="3" spans="1:10" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="59" t="s">
+      <c r="C3" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="59" t="s">
+      <c r="D3" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="60">
+      <c r="E3" s="59">
         <v>45955</v>
       </c>
-      <c r="F3" s="60">
+      <c r="F3" s="59">
         <v>45977</v>
       </c>
-      <c r="G3" s="59">
+      <c r="G3" s="58">
         <f>F3-E3</f>
         <v>22</v>
       </c>
-      <c r="H3" s="59">
+      <c r="H3" s="58">
         <v>10</v>
       </c>
-      <c r="I3" s="61">
+      <c r="I3" s="60">
         <f>J3/H3</f>
         <v>1</v>
       </c>
-      <c r="J3" s="59">
+      <c r="J3" s="58">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="59" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="59" t="s">
+    <row r="4" spans="1:10" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="59" t="s">
+      <c r="B4" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="59" t="s">
+      <c r="D4" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="E4" s="60">
+      <c r="E4" s="59">
         <v>45982</v>
       </c>
-      <c r="F4" s="60">
+      <c r="F4" s="59">
         <v>46003</v>
       </c>
-      <c r="G4" s="59">
+      <c r="G4" s="58">
         <f>F4-E4</f>
         <v>21</v>
       </c>
-      <c r="H4" s="59">
+      <c r="H4" s="58">
         <v>10</v>
       </c>
-      <c r="I4" s="61">
+      <c r="I4" s="60">
         <f>J4/H4</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="62" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="59" t="s">
+    <row r="5" spans="1:10" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="62" t="s">
+      <c r="B5" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="62" t="s">
+      <c r="C5" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="62" t="s">
+      <c r="D5" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="63">
+      <c r="E5" s="62">
         <v>46005</v>
       </c>
-      <c r="F5" s="63">
+      <c r="F5" s="62">
         <v>46026</v>
       </c>
-      <c r="G5" s="62">
+      <c r="G5" s="61">
         <f>F5-E5</f>
         <v>21</v>
       </c>
-      <c r="H5" s="62">
+      <c r="H5" s="61">
         <v>10</v>
       </c>
-      <c r="I5" s="64" t="e">
+      <c r="I5" s="63" t="e">
         <f>#REF!/H5</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="62" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="62" t="s">
+    <row r="6" spans="1:10" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="62" t="s">
+      <c r="B6" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="62" t="s">
+      <c r="C6" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="63">
+      <c r="E6" s="62">
         <v>46015</v>
       </c>
-      <c r="F6" s="63">
+      <c r="F6" s="62">
         <v>46036</v>
       </c>
-      <c r="G6" s="62">
+      <c r="G6" s="61">
         <f>F6-E6</f>
         <v>21</v>
       </c>
-      <c r="H6" s="62">
+      <c r="H6" s="61">
         <v>10</v>
       </c>
-      <c r="I6" s="64">
+      <c r="I6" s="63">
         <f>J6/H6</f>
         <v>0.9</v>
       </c>
-      <c r="J6" s="62">
+      <c r="J6" s="61">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="65" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
-    </row>
-    <row r="9" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="67" t="s">
+    <row r="7" spans="1:10" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+    </row>
+    <row r="9" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="67" t="s">
+      <c r="B9" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="67" t="s">
+      <c r="C9" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="67" t="s">
+      <c r="D9" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="68">
+      <c r="E9" s="65">
         <v>46106</v>
       </c>
-      <c r="F9" s="68">
+      <c r="F9" s="65">
         <v>46129</v>
       </c>
-      <c r="G9" s="67">
+      <c r="G9" s="64">
         <f>F9-E9</f>
         <v>23</v>
       </c>
-      <c r="H9" s="67">
+      <c r="H9" s="64">
         <v>13</v>
       </c>
-      <c r="I9" s="69">
+      <c r="I9" s="66">
         <f>J9/H9</f>
         <v>0.61538461538461542</v>
       </c>
-      <c r="J9" s="67">
+      <c r="J9" s="64">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="67" t="s">
+    <row r="10" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="67" t="s">
+      <c r="B10" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="67" t="s">
+      <c r="C10" s="64" t="s">
         <v>85</v>
       </c>
-      <c r="D10" s="67" t="s">
+      <c r="D10" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="68">
+      <c r="E10" s="65">
         <v>46106</v>
       </c>
-      <c r="F10" s="68">
+      <c r="F10" s="65">
         <v>46129</v>
       </c>
-      <c r="G10" s="67">
+      <c r="G10" s="64">
         <f>F10-E10</f>
         <v>23</v>
       </c>
-      <c r="H10" s="67">
+      <c r="H10" s="64">
         <v>13</v>
       </c>
-      <c r="I10" s="69">
+      <c r="I10" s="66">
         <f>J10/H10</f>
         <v>0.23076923076923078</v>
       </c>
-      <c r="J10" s="67">
+      <c r="J10" s="64">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="67" t="s">
+    <row r="11" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="67" t="s">
+      <c r="B11" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="67" t="s">
+      <c r="C11" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="D11" s="67" t="s">
+      <c r="D11" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="68">
+      <c r="E11" s="65">
         <v>46122</v>
       </c>
-      <c r="F11" s="68">
+      <c r="F11" s="65">
         <v>46144</v>
       </c>
-      <c r="G11" s="67">
+      <c r="G11" s="64">
         <f>F11-E11</f>
         <v>22</v>
       </c>
-      <c r="H11" s="67">
+      <c r="H11" s="64">
         <v>13</v>
       </c>
-      <c r="I11" s="69">
+      <c r="I11" s="66">
         <f>J11/H11</f>
         <v>0.38461538461538464</v>
       </c>
-      <c r="J11" s="67">
+      <c r="J11" s="64">
         <v>5</v>
       </c>
     </row>
@@ -3748,379 +3739,404 @@
       <c r="F13" s="16"/>
       <c r="I13" s="33"/>
     </row>
-    <row r="14" spans="1:10" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="80" t="s">
+    <row r="14" spans="1:10" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="77" t="s">
         <v>88</v>
       </c>
-      <c r="C14" s="80" t="s">
+      <c r="C14" s="77" t="s">
         <v>89</v>
       </c>
-      <c r="D14" s="80" t="s">
+      <c r="D14" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="81">
+      <c r="E14" s="79">
         <v>46159</v>
       </c>
-      <c r="F14" s="81">
+      <c r="F14" s="79">
         <v>46182</v>
       </c>
-      <c r="G14" s="82">
+      <c r="G14" s="77">
         <f>F14-E14</f>
         <v>23</v>
       </c>
-      <c r="H14" s="80">
+      <c r="H14" s="77">
         <v>12</v>
       </c>
-      <c r="I14" s="83">
+      <c r="I14" s="77">
         <f>J14/H14</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="J14" s="80">
+      <c r="J14" s="77">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:10" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="80" t="s">
+    <row r="15" spans="1:10" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="77" t="s">
         <v>90</v>
       </c>
-      <c r="C15" s="80" t="s">
+      <c r="C15" s="77" t="s">
         <v>91</v>
       </c>
-      <c r="D15" s="80" t="s">
+      <c r="D15" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="81">
+      <c r="E15" s="79">
         <v>46169</v>
       </c>
-      <c r="F15" s="81">
+      <c r="F15" s="79">
         <v>46190</v>
       </c>
-      <c r="G15" s="82">
+      <c r="G15" s="77">
         <f>F15-E15</f>
         <v>21</v>
       </c>
-      <c r="H15" s="80">
+      <c r="H15" s="77">
         <v>12</v>
       </c>
-      <c r="I15" s="83" t="s">
+      <c r="I15" s="77" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="80" t="s">
+    <row r="16" spans="1:10" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="77" t="s">
         <v>90</v>
       </c>
-      <c r="C16" s="80" t="s">
+      <c r="C16" s="77" t="s">
         <v>91</v>
       </c>
-      <c r="D16" s="80" t="s">
+      <c r="D16" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="81">
+      <c r="E16" s="79">
         <v>46171</v>
       </c>
-      <c r="F16" s="81">
+      <c r="F16" s="79">
         <v>46184</v>
       </c>
-      <c r="G16" s="82">
+      <c r="G16" s="77">
         <f>F16-E16</f>
         <v>13</v>
       </c>
-      <c r="H16" s="80">
+      <c r="H16" s="77">
         <v>3</v>
       </c>
-      <c r="I16" s="83">
+      <c r="I16" s="77">
         <f>J16/H16</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="J16" s="80">
+      <c r="J16" s="77">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11" s="76" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="80" t="s">
+    <row r="17" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="80" t="s">
+      <c r="D17" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="81">
+      <c r="E17" s="79">
         <v>46188</v>
       </c>
-      <c r="F17" s="81">
+      <c r="F17" s="79">
         <v>46209</v>
       </c>
-      <c r="G17" s="82">
+      <c r="G17" s="77">
         <f>F17-E17</f>
         <v>21</v>
       </c>
-      <c r="H17" s="80">
+      <c r="H17" s="77">
         <v>12</v>
       </c>
-      <c r="I17" s="83">
+      <c r="I17" s="77">
         <f>J17/H17</f>
         <v>1</v>
       </c>
-      <c r="J17" s="80">
+      <c r="J17" s="77">
         <v>12</v>
       </c>
-      <c r="K17" s="80"/>
-    </row>
-    <row r="18" spans="1:11" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="80" t="s">
+      <c r="K17" s="77"/>
+    </row>
+    <row r="18" spans="1:11" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="80" t="s">
+      <c r="B18" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="80" t="s">
+      <c r="C18" s="77" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="80" t="s">
+      <c r="D18" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="E18" s="81">
+      <c r="E18" s="79">
         <v>46194</v>
       </c>
-      <c r="F18" s="81">
+      <c r="F18" s="79">
         <v>46215</v>
       </c>
-      <c r="G18" s="82">
+      <c r="G18" s="77">
         <f>F18-E18</f>
         <v>21</v>
       </c>
-      <c r="H18" s="80">
+      <c r="H18" s="77">
         <v>12</v>
       </c>
-      <c r="I18" s="83">
+      <c r="I18" s="77">
         <f>J18/H18</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="J18" s="80">
+      <c r="J18" s="77">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:11" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="80" t="s">
+    <row r="19" spans="1:11" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="80" t="s">
+      <c r="B19" s="77" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:11" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="80" t="s">
+    <row r="20" spans="1:11" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="80" t="s">
+      <c r="C20" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="D20" s="80" t="s">
+      <c r="D20" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="81">
+      <c r="E20" s="79">
         <v>46221</v>
       </c>
-      <c r="F20" s="81">
+      <c r="F20" s="79">
         <v>46245</v>
       </c>
-      <c r="G20" s="82">
+      <c r="G20" s="77">
         <f>F20-E20</f>
         <v>24</v>
       </c>
-      <c r="H20" s="80">
+      <c r="H20" s="77">
         <v>12</v>
       </c>
-      <c r="I20" s="83">
+      <c r="I20" s="77">
         <f>J20/H20</f>
         <v>0.91666666666666663</v>
       </c>
-      <c r="J20" s="80">
+      <c r="J20" s="77">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:11" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="80" t="s">
+    <row r="21" spans="1:11" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="80" t="s">
+      <c r="C21" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="80" t="s">
+      <c r="D21" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="81">
+      <c r="E21" s="79">
         <v>46223</v>
       </c>
-      <c r="F21" s="81">
+      <c r="F21" s="79">
         <v>46245</v>
       </c>
-      <c r="G21" s="82">
+      <c r="G21" s="77">
         <f>F21-E21</f>
         <v>22</v>
       </c>
-      <c r="H21" s="80">
+      <c r="H21" s="77">
         <v>12</v>
       </c>
-      <c r="I21" s="83">
+      <c r="I21" s="77">
         <f>J21/H21</f>
         <v>0.58333333333333337</v>
       </c>
-      <c r="J21" s="80">
+      <c r="J21" s="77">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="84" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="17" t="s">
+    <row r="22" spans="1:11" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="77" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="79" t="s">
         <v>98</v>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="79">
         <f t="shared" ref="F22" ca="1" si="0">TODAY()</f>
-        <v>46273</v>
-      </c>
-      <c r="G22" s="17" t="e">
+        <v>46291</v>
+      </c>
+      <c r="G22" s="77" t="e">
         <f t="shared" ref="G22:G23" ca="1" si="1">F22-E22</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H22" s="17"/>
-      <c r="I22" s="22" t="e">
+      <c r="I22" s="77" t="e">
         <f t="shared" ref="I22:I23" si="2">J22/H22</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J22" s="17"/>
-      <c r="K22" s="22"/>
-    </row>
-    <row r="23" spans="1:11" s="80" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="80" t="s">
+    </row>
+    <row r="23" spans="1:11" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="80" t="s">
+      <c r="C23" s="77" t="s">
         <v>97</v>
       </c>
-      <c r="D23" s="80" t="s">
+      <c r="D23" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="E23" s="81">
+      <c r="E23" s="79">
         <v>46237</v>
       </c>
-      <c r="F23" s="81">
+      <c r="F23" s="79">
         <v>46260</v>
       </c>
-      <c r="G23" s="82">
+      <c r="G23" s="77">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="H23" s="80">
+      <c r="H23" s="77">
         <v>10</v>
       </c>
-      <c r="I23" s="22">
+      <c r="I23" s="77">
         <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
-      <c r="J23" s="80">
+      <c r="J23" s="77">
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B24" s="72"/>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="73"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="72"/>
-      <c r="J24" s="72"/>
-      <c r="K24" s="22"/>
-    </row>
-    <row r="25" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="30" t="s">
+    <row r="24" spans="1:11" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="78" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="78" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="80">
+        <v>46290</v>
+      </c>
+      <c r="F24" s="80">
+        <v>46311</v>
+      </c>
+      <c r="G24" s="78">
+        <f>F24-E24</f>
+        <v>21</v>
+      </c>
+      <c r="H24" s="78">
+        <v>12</v>
+      </c>
+      <c r="I24" s="78">
+        <f>J24/H24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B25" s="69"/>
+      <c r="C25" s="69"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="69"/>
+      <c r="J25" s="69"/>
+      <c r="K25" s="22"/>
+    </row>
+    <row r="26" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="30" t="s">
+      <c r="B26" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="30" t="s">
+      <c r="C26" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="31" t="s">
+      <c r="D26" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E26" s="31">
         <v>45996</v>
       </c>
-      <c r="F25" s="31"/>
-      <c r="I25" s="32"/>
-    </row>
-    <row r="27" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="59"/>
-      <c r="B27" s="62" t="s">
+      <c r="F26" s="31"/>
+      <c r="I26" s="32"/>
+    </row>
+    <row r="28" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="58"/>
+      <c r="B28" s="61" t="s">
         <v>80</v>
       </c>
-      <c r="C27" s="62" t="s">
+      <c r="C28" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="D27" s="62" t="s">
+      <c r="D28" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="E27" s="63">
+      <c r="E28" s="62">
         <v>46060</v>
       </c>
-      <c r="F27" s="63">
+      <c r="F28" s="62">
         <v>46081</v>
       </c>
-      <c r="G27" s="62">
-        <f>F27-E27</f>
-        <v>21</v>
-      </c>
-      <c r="H27" s="62">
-        <v>12</v>
-      </c>
-      <c r="I27" s="64">
-        <f>J27/H27</f>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J27" s="62">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" s="62" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="62" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="62" t="s">
-        <v>29</v>
-      </c>
-      <c r="E28" s="63">
-        <v>46067</v>
-      </c>
-      <c r="F28" s="63">
-        <v>46088</v>
-      </c>
-      <c r="G28" s="62">
+      <c r="G28" s="61">
         <f>F28-E28</f>
         <v>21</v>
       </c>
-      <c r="H28" s="62">
+      <c r="H28" s="61">
         <v>12</v>
       </c>
-      <c r="I28" s="64">
+      <c r="I28" s="63">
         <f>J28/H28</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J28" s="61">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="61" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" s="62">
+        <v>46067</v>
+      </c>
+      <c r="F29" s="62">
+        <v>46088</v>
+      </c>
+      <c r="G29" s="61">
+        <f>F29-E29</f>
+        <v>21</v>
+      </c>
+      <c r="H29" s="61">
+        <v>12</v>
+      </c>
+      <c r="I29" s="63">
+        <f>J29/H29</f>
         <v>0.41666666666666669</v>
       </c>
-      <c r="J28" s="62">
+      <c r="J29" s="61">
         <v>5</v>
       </c>
     </row>
@@ -4192,16 +4208,16 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46291</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="H2" s="55"/>
+      <c r="H2" s="54"/>
       <c r="I2" s="19">
         <v>1</v>
       </c>
@@ -4224,16 +4240,16 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46273</v>
+        <v>46291</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="H3" s="55"/>
+      <c r="H3" s="54"/>
       <c r="I3" s="19">
         <v>1</v>
       </c>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155279F8-4E6C-49D3-9358-553CC24EBD9E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062568B3-39D2-459C-B4CA-589F1F54773D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="102">
   <si>
     <t>HOJE</t>
   </si>
@@ -331,6 +331,12 @@
   </si>
   <si>
     <t>Filó</t>
+  </si>
+  <si>
+    <t>SH</t>
+  </si>
+  <si>
+    <t>Sheila</t>
   </si>
 </sst>
 </file>
@@ -1125,7 +1131,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1402,11 +1408,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1509,18 +1515,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>2.8925619834710745E-2</v>
+        <v>2.88659793814433E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
@@ -1620,18 +1626,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>3.6319612590799029E-2</v>
+        <v>3.6231884057971016E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1694,7 +1700,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-381</v>
+        <v>-382</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1729,7 +1735,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-381</v>
+        <v>-382</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1784,18 +1790,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>7.7519379844961239E-3</v>
+        <v>7.7319587628865982E-3</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1816,7 +1822,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1847,18 +1853,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>7.7519379844961239E-3</v>
+        <v>7.7319587628865982E-3</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1879,18 +1885,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>7.7519379844961239E-3</v>
+        <v>7.7319587628865982E-3</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2231,14 +2237,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2263,14 +2269,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2295,14 +2301,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2327,14 +2333,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2393,18 +2399,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="54">
         <f ca="1">F46*2</f>
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2428,18 +2434,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="54">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2463,18 +2469,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="54">
         <f t="shared" ca="1" si="12"/>
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2546,14 +2552,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2711,7 +2717,7 @@
       <c r="C1" s="46"/>
       <c r="D1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F1" s="46"/>
       <c r="G1" s="46"/>
@@ -2779,14 +2785,14 @@
       </c>
       <c r="F3" s="65">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="G3" s="65">
         <v>45947</v>
       </c>
       <c r="H3" s="64">
         <f t="shared" ref="H3:H8" ca="1" si="0">F3-G3</f>
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="I3" s="64" t="s">
         <v>54</v>
@@ -2820,14 +2826,14 @@
       </c>
       <c r="F4" s="65">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="G4" s="65">
         <v>45953</v>
       </c>
       <c r="H4" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I4" s="64" t="s">
         <v>54</v>
@@ -2861,14 +2867,14 @@
       </c>
       <c r="F5" s="65">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="G5" s="65">
         <v>45956</v>
       </c>
       <c r="H5" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="I5" s="64" t="s">
         <v>54</v>
@@ -2903,14 +2909,14 @@
       </c>
       <c r="F6" s="68">
         <f t="shared" ref="F6:F14" ca="1" si="2">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="G6" s="68">
         <v>45910</v>
       </c>
       <c r="H6" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="I6" s="67" t="s">
         <v>54</v>
@@ -2945,14 +2951,14 @@
       </c>
       <c r="F7" s="65">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="G7" s="65">
         <v>46027</v>
       </c>
       <c r="H7" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I7" s="64" t="s">
         <v>54</v>
@@ -2986,14 +2992,14 @@
       </c>
       <c r="F8" s="72">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="G8" s="72">
         <v>46036</v>
       </c>
       <c r="H8" s="71">
         <f t="shared" ca="1" si="0"/>
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I8" s="71" t="s">
         <v>54</v>
@@ -3027,14 +3033,14 @@
       </c>
       <c r="F9" s="72">
         <f t="shared" ca="1" si="2"/>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="G9" s="72">
         <v>46082</v>
       </c>
       <c r="H9" s="71">
         <f ca="1">F9-G9</f>
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I9" s="71" t="s">
         <v>54</v>
@@ -3068,14 +3074,14 @@
       </c>
       <c r="F10" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="G10" s="18">
         <v>46089</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" ref="H10:H17" ca="1" si="3">F10-G10</f>
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>54</v>
@@ -3109,14 +3115,14 @@
       </c>
       <c r="F11" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="G11" s="70">
         <v>46129</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I11" s="17" t="s">
         <v>54</v>
@@ -3144,14 +3150,14 @@
       </c>
       <c r="F12" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="G12" s="70">
         <v>46129</v>
       </c>
       <c r="H12" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>54</v>
@@ -3179,14 +3185,14 @@
       </c>
       <c r="F13" s="72">
         <f t="shared" ca="1" si="2"/>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="G13" s="72">
         <v>46182</v>
       </c>
       <c r="H13" s="71">
         <f t="shared" ca="1" si="3"/>
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I13" s="71" t="s">
         <v>54</v>
@@ -3214,14 +3220,14 @@
       </c>
       <c r="F14" s="72">
         <f t="shared" ca="1" si="2"/>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="G14" s="72">
         <v>46184</v>
       </c>
       <c r="H14" s="71">
         <f t="shared" ca="1" si="3"/>
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I14" s="71" t="s">
         <v>54</v>
@@ -3249,14 +3255,14 @@
       </c>
       <c r="F15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="G15" s="18">
         <v>46216</v>
       </c>
       <c r="H15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I15" s="69" t="s">
         <v>54</v>
@@ -3284,11 +3290,11 @@
       </c>
       <c r="F16" s="72">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="G16" s="72">
         <f t="shared" ref="G16" ca="1" si="4">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="H16" s="71">
         <f t="shared" ca="1" si="3"/>
@@ -3320,14 +3326,14 @@
       </c>
       <c r="F17" s="18">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="G17" s="18">
         <v>46271</v>
       </c>
       <c r="H17" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I17" s="69" t="s">
         <v>54</v>
@@ -3398,7 +3404,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21D6C99-536E-4F31-8A16-5ECA51AF8689}">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" style="21" customWidth="1"/>
@@ -3420,7 +3426,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3976,7 +3982,7 @@
       </c>
       <c r="F22" s="79">
         <f t="shared" ref="F22" ca="1" si="0">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="G22" s="77" t="e">
         <f t="shared" ref="G22:G23" ca="1" si="1">F22-E22</f>
@@ -4046,84 +4052,81 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="69"/>
-      <c r="C25" s="69"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="70"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="69"/>
-      <c r="J25" s="69"/>
-      <c r="K25" s="22"/>
-    </row>
-    <row r="26" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="30" t="s">
+    <row r="25" spans="1:11" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25" s="78" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" s="78" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="80">
+        <v>46291</v>
+      </c>
+      <c r="F25" s="80">
+        <v>46312</v>
+      </c>
+      <c r="G25" s="78">
+        <f>F25-E25</f>
+        <v>21</v>
+      </c>
+      <c r="H25" s="78">
+        <v>12</v>
+      </c>
+      <c r="I25" s="78">
+        <f>J25/H25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B26" s="69"/>
+      <c r="C26" s="69"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="69"/>
+      <c r="J26" s="69"/>
+      <c r="K26" s="22"/>
+    </row>
+    <row r="27" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B26" s="30" t="s">
+      <c r="B27" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="30" t="s">
+      <c r="C27" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="31" t="s">
+      <c r="D27" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="E26" s="31">
+      <c r="E27" s="31">
         <v>45996</v>
       </c>
-      <c r="F26" s="31"/>
-      <c r="I26" s="32"/>
-    </row>
-    <row r="28" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="58"/>
-      <c r="B28" s="61" t="s">
+      <c r="F27" s="31"/>
+      <c r="I27" s="32"/>
+    </row>
+    <row r="29" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="58"/>
+      <c r="B29" s="61" t="s">
         <v>80</v>
       </c>
-      <c r="C28" s="61" t="s">
+      <c r="C29" s="61" t="s">
         <v>81</v>
-      </c>
-      <c r="D28" s="61" t="s">
-        <v>29</v>
-      </c>
-      <c r="E28" s="62">
-        <v>46060</v>
-      </c>
-      <c r="F28" s="62">
-        <v>46081</v>
-      </c>
-      <c r="G28" s="61">
-        <f>F28-E28</f>
-        <v>21</v>
-      </c>
-      <c r="H28" s="61">
-        <v>12</v>
-      </c>
-      <c r="I28" s="63">
-        <f>J28/H28</f>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J28" s="61">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="61" t="s">
-        <v>8</v>
       </c>
       <c r="D29" s="61" t="s">
         <v>29</v>
       </c>
       <c r="E29" s="62">
-        <v>46067</v>
+        <v>46060</v>
       </c>
       <c r="F29" s="62">
-        <v>46088</v>
+        <v>46081</v>
       </c>
       <c r="G29" s="61">
         <f>F29-E29</f>
@@ -4134,9 +4137,40 @@
       </c>
       <c r="I29" s="63">
         <f>J29/H29</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J29" s="61">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="61" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30" s="62">
+        <v>46067</v>
+      </c>
+      <c r="F30" s="62">
+        <v>46088</v>
+      </c>
+      <c r="G30" s="61">
+        <f>F30-E30</f>
+        <v>21</v>
+      </c>
+      <c r="H30" s="61">
+        <v>12</v>
+      </c>
+      <c r="I30" s="63">
+        <f>J30/H30</f>
         <v>0.41666666666666669</v>
       </c>
-      <c r="J29" s="61">
+      <c r="J30" s="61">
         <v>5</v>
       </c>
     </row>
@@ -4208,11 +4242,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -4240,11 +4274,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{062568B3-39D2-459C-B4CA-589F1F54773D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA6B063-D263-436B-9D38-2B547C48ADBD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="102">
   <si>
     <t>HOJE</t>
   </si>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1408,11 +1408,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1515,18 +1515,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>2.88659793814433E-2</v>
+        <v>2.8571428571428571E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
@@ -1626,18 +1626,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>3.6231884057971016E-2</v>
+        <v>3.5799522673031027E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-382</v>
+        <v>-387</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-382</v>
+        <v>-387</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1790,18 +1790,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>7.7319587628865982E-3</v>
+        <v>7.6335877862595417E-3</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1853,18 +1853,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>7.7319587628865982E-3</v>
+        <v>7.6335877862595417E-3</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1885,18 +1885,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>7.7319587628865982E-3</v>
+        <v>7.6335877862595417E-3</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2237,14 +2237,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2269,14 +2269,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2301,14 +2301,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2333,14 +2333,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2399,18 +2399,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="54">
         <f ca="1">F46*2</f>
-        <v>966</v>
+        <v>976</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2434,18 +2434,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="54">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>698</v>
+        <v>708</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2469,18 +2469,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="54">
         <f t="shared" ca="1" si="12"/>
-        <v>662</v>
+        <v>672</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2552,14 +2552,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2717,7 +2717,7 @@
       <c r="C1" s="46"/>
       <c r="D1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="F1" s="46"/>
       <c r="G1" s="46"/>
@@ -2785,14 +2785,14 @@
       </c>
       <c r="F3" s="65">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="G3" s="65">
         <v>45947</v>
       </c>
       <c r="H3" s="64">
         <f t="shared" ref="H3:H8" ca="1" si="0">F3-G3</f>
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="I3" s="64" t="s">
         <v>54</v>
@@ -2826,14 +2826,14 @@
       </c>
       <c r="F4" s="65">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="G4" s="65">
         <v>45953</v>
       </c>
       <c r="H4" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I4" s="64" t="s">
         <v>54</v>
@@ -2867,14 +2867,14 @@
       </c>
       <c r="F5" s="65">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="G5" s="65">
         <v>45956</v>
       </c>
       <c r="H5" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="I5" s="64" t="s">
         <v>54</v>
@@ -2909,14 +2909,14 @@
       </c>
       <c r="F6" s="68">
         <f t="shared" ref="F6:F14" ca="1" si="2">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="G6" s="68">
         <v>45910</v>
       </c>
       <c r="H6" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I6" s="67" t="s">
         <v>54</v>
@@ -2951,14 +2951,14 @@
       </c>
       <c r="F7" s="65">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="G7" s="65">
         <v>46027</v>
       </c>
       <c r="H7" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="I7" s="64" t="s">
         <v>54</v>
@@ -2992,14 +2992,14 @@
       </c>
       <c r="F8" s="72">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="G8" s="72">
         <v>46036</v>
       </c>
       <c r="H8" s="71">
         <f t="shared" ca="1" si="0"/>
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="I8" s="71" t="s">
         <v>54</v>
@@ -3033,14 +3033,14 @@
       </c>
       <c r="F9" s="72">
         <f t="shared" ca="1" si="2"/>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="G9" s="72">
         <v>46082</v>
       </c>
       <c r="H9" s="71">
         <f ca="1">F9-G9</f>
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="I9" s="71" t="s">
         <v>54</v>
@@ -3074,14 +3074,14 @@
       </c>
       <c r="F10" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="G10" s="18">
         <v>46089</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" ref="H10:H17" ca="1" si="3">F10-G10</f>
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>54</v>
@@ -3115,14 +3115,14 @@
       </c>
       <c r="F11" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="G11" s="70">
         <v>46129</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I11" s="17" t="s">
         <v>54</v>
@@ -3150,14 +3150,14 @@
       </c>
       <c r="F12" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="G12" s="70">
         <v>46129</v>
       </c>
       <c r="H12" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>54</v>
@@ -3185,14 +3185,14 @@
       </c>
       <c r="F13" s="72">
         <f t="shared" ca="1" si="2"/>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="G13" s="72">
         <v>46182</v>
       </c>
       <c r="H13" s="71">
         <f t="shared" ca="1" si="3"/>
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I13" s="71" t="s">
         <v>54</v>
@@ -3220,14 +3220,14 @@
       </c>
       <c r="F14" s="72">
         <f t="shared" ca="1" si="2"/>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="G14" s="72">
         <v>46184</v>
       </c>
       <c r="H14" s="71">
         <f t="shared" ca="1" si="3"/>
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I14" s="71" t="s">
         <v>54</v>
@@ -3255,14 +3255,14 @@
       </c>
       <c r="F15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="G15" s="18">
         <v>46216</v>
       </c>
       <c r="H15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I15" s="69" t="s">
         <v>54</v>
@@ -3290,11 +3290,11 @@
       </c>
       <c r="F16" s="72">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="G16" s="72">
         <f t="shared" ref="G16" ca="1" si="4">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="H16" s="71">
         <f t="shared" ca="1" si="3"/>
@@ -3326,14 +3326,14 @@
       </c>
       <c r="F17" s="18">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="G17" s="18">
         <v>46271</v>
       </c>
       <c r="H17" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="I17" s="69" t="s">
         <v>54</v>
@@ -3404,7 +3404,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21D6C99-536E-4F31-8A16-5ECA51AF8689}">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" style="21" customWidth="1"/>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3868,7 +3868,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="77" t="s">
-        <v>7</v>
+        <v>95</v>
       </c>
       <c r="C18" s="77" t="s">
         <v>94</v>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="F22" s="79">
         <f t="shared" ref="F22" ca="1" si="0">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="G22" s="77" t="e">
         <f t="shared" ref="G22:G23" ca="1" si="1">F22-E22</f>
@@ -4080,84 +4080,84 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="69"/>
-      <c r="C26" s="69"/>
-      <c r="D26" s="69"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="70"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="69"/>
-      <c r="J26" s="69"/>
-      <c r="K26" s="22"/>
-    </row>
-    <row r="27" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="30" t="s">
+    <row r="26" spans="1:11" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="78" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="78" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" s="78" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="78" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="80">
+        <v>46297</v>
+      </c>
+      <c r="F26" s="80">
+        <v>46318</v>
+      </c>
+      <c r="G26" s="78">
+        <f>F26-E26</f>
+        <v>21</v>
+      </c>
+      <c r="H26" s="78">
+        <v>12</v>
+      </c>
+      <c r="I26" s="78">
+        <f>J26/H26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B27" s="69"/>
+      <c r="C27" s="69"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="69"/>
+      <c r="J27" s="69"/>
+      <c r="K27" s="22"/>
+    </row>
+    <row r="28" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B27" s="30" t="s">
+      <c r="B28" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="30" t="s">
+      <c r="C28" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="31" t="s">
+      <c r="D28" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E28" s="31">
         <v>45996</v>
       </c>
-      <c r="F27" s="31"/>
-      <c r="I27" s="32"/>
-    </row>
-    <row r="29" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="58"/>
-      <c r="B29" s="61" t="s">
+      <c r="F28" s="31"/>
+      <c r="I28" s="32"/>
+    </row>
+    <row r="30" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="58"/>
+      <c r="B30" s="61" t="s">
         <v>80</v>
       </c>
-      <c r="C29" s="61" t="s">
+      <c r="C30" s="61" t="s">
         <v>81</v>
-      </c>
-      <c r="D29" s="61" t="s">
-        <v>29</v>
-      </c>
-      <c r="E29" s="62">
-        <v>46060</v>
-      </c>
-      <c r="F29" s="62">
-        <v>46081</v>
-      </c>
-      <c r="G29" s="61">
-        <f>F29-E29</f>
-        <v>21</v>
-      </c>
-      <c r="H29" s="61">
-        <v>12</v>
-      </c>
-      <c r="I29" s="63">
-        <f>J29/H29</f>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J29" s="61">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="61" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="61" t="s">
-        <v>8</v>
       </c>
       <c r="D30" s="61" t="s">
         <v>29</v>
       </c>
       <c r="E30" s="62">
-        <v>46067</v>
+        <v>46060</v>
       </c>
       <c r="F30" s="62">
-        <v>46088</v>
+        <v>46081</v>
       </c>
       <c r="G30" s="61">
         <f>F30-E30</f>
@@ -4168,9 +4168,40 @@
       </c>
       <c r="I30" s="63">
         <f>J30/H30</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J30" s="61">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="61" t="s">
+        <v>29</v>
+      </c>
+      <c r="E31" s="62">
+        <v>46067</v>
+      </c>
+      <c r="F31" s="62">
+        <v>46088</v>
+      </c>
+      <c r="G31" s="61">
+        <f>F31-E31</f>
+        <v>21</v>
+      </c>
+      <c r="H31" s="61">
+        <v>12</v>
+      </c>
+      <c r="I31" s="63">
+        <f>J31/H31</f>
         <v>0.41666666666666669</v>
       </c>
-      <c r="J30" s="61">
+      <c r="J31" s="61">
         <v>5</v>
       </c>
     </row>
@@ -4242,11 +4273,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -4274,11 +4305,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA6B063-D263-436B-9D38-2B547C48ADBD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7534A965-FF61-417D-AA4A-0DA497E9B255}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="102">
   <si>
     <t>HOJE</t>
   </si>
@@ -550,7 +550,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -793,6 +793,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1131,7 +1137,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1408,11 +1414,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1515,18 +1521,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>490</v>
+        <v>510</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>2.8571428571428571E-2</v>
+        <v>2.7450980392156862E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
@@ -1626,18 +1632,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>3.5799522673031027E-2</v>
+        <v>3.4168564920273349E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1700,7 +1706,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-387</v>
+        <v>-407</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1735,7 +1741,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-387</v>
+        <v>-407</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1790,18 +1796,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>7.6335877862595417E-3</v>
+        <v>7.2639225181598066E-3</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1822,7 +1828,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1853,18 +1859,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>7.6335877862595417E-3</v>
+        <v>7.2639225181598066E-3</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1885,18 +1891,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>7.6335877862595417E-3</v>
+        <v>7.2639225181598066E-3</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2237,14 +2243,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2269,14 +2275,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2301,14 +2307,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2333,14 +2339,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2399,18 +2405,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>488</v>
+        <v>508</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="54">
         <f ca="1">F46*2</f>
-        <v>976</v>
+        <v>1016</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2434,18 +2440,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>354</v>
+        <v>374</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="54">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>708</v>
+        <v>748</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2469,18 +2475,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="54">
         <f t="shared" ca="1" si="12"/>
-        <v>672</v>
+        <v>712</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2552,14 +2558,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2717,7 +2723,7 @@
       <c r="C1" s="46"/>
       <c r="D1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="F1" s="46"/>
       <c r="G1" s="46"/>
@@ -2785,14 +2791,14 @@
       </c>
       <c r="F3" s="65">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="G3" s="65">
         <v>45947</v>
       </c>
       <c r="H3" s="64">
         <f t="shared" ref="H3:H8" ca="1" si="0">F3-G3</f>
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="I3" s="64" t="s">
         <v>54</v>
@@ -2826,14 +2832,14 @@
       </c>
       <c r="F4" s="65">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="G4" s="65">
         <v>45953</v>
       </c>
       <c r="H4" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>344</v>
+        <v>364</v>
       </c>
       <c r="I4" s="64" t="s">
         <v>54</v>
@@ -2867,14 +2873,14 @@
       </c>
       <c r="F5" s="65">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="G5" s="65">
         <v>45956</v>
       </c>
       <c r="H5" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="I5" s="64" t="s">
         <v>54</v>
@@ -2909,14 +2915,14 @@
       </c>
       <c r="F6" s="68">
         <f t="shared" ref="F6:F14" ca="1" si="2">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="G6" s="68">
         <v>45910</v>
       </c>
       <c r="H6" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="I6" s="67" t="s">
         <v>54</v>
@@ -2951,14 +2957,14 @@
       </c>
       <c r="F7" s="65">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="G7" s="65">
         <v>46027</v>
       </c>
       <c r="H7" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="I7" s="64" t="s">
         <v>54</v>
@@ -2992,14 +2998,14 @@
       </c>
       <c r="F8" s="72">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="G8" s="72">
         <v>46036</v>
       </c>
       <c r="H8" s="71">
         <f t="shared" ca="1" si="0"/>
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="I8" s="71" t="s">
         <v>54</v>
@@ -3033,14 +3039,14 @@
       </c>
       <c r="F9" s="72">
         <f t="shared" ca="1" si="2"/>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="G9" s="72">
         <v>46082</v>
       </c>
       <c r="H9" s="71">
         <f ca="1">F9-G9</f>
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="I9" s="71" t="s">
         <v>54</v>
@@ -3074,14 +3080,14 @@
       </c>
       <c r="F10" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="G10" s="18">
         <v>46089</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" ref="H10:H17" ca="1" si="3">F10-G10</f>
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>54</v>
@@ -3115,14 +3121,14 @@
       </c>
       <c r="F11" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="G11" s="70">
         <v>46129</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="I11" s="17" t="s">
         <v>54</v>
@@ -3150,14 +3156,14 @@
       </c>
       <c r="F12" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="G12" s="70">
         <v>46129</v>
       </c>
       <c r="H12" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>54</v>
@@ -3185,14 +3191,14 @@
       </c>
       <c r="F13" s="72">
         <f t="shared" ca="1" si="2"/>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="G13" s="72">
         <v>46182</v>
       </c>
       <c r="H13" s="71">
         <f t="shared" ca="1" si="3"/>
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="I13" s="71" t="s">
         <v>54</v>
@@ -3220,14 +3226,14 @@
       </c>
       <c r="F14" s="72">
         <f t="shared" ca="1" si="2"/>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="G14" s="72">
         <v>46184</v>
       </c>
       <c r="H14" s="71">
         <f t="shared" ca="1" si="3"/>
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="I14" s="71" t="s">
         <v>54</v>
@@ -3255,14 +3261,14 @@
       </c>
       <c r="F15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="G15" s="18">
         <v>46216</v>
       </c>
       <c r="H15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="I15" s="69" t="s">
         <v>54</v>
@@ -3290,11 +3296,11 @@
       </c>
       <c r="F16" s="72">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="G16" s="72">
         <f t="shared" ref="G16" ca="1" si="4">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="H16" s="71">
         <f t="shared" ca="1" si="3"/>
@@ -3326,14 +3332,14 @@
       </c>
       <c r="F17" s="18">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="G17" s="18">
         <v>46271</v>
       </c>
       <c r="H17" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I17" s="69" t="s">
         <v>54</v>
@@ -3388,6 +3394,34 @@
       </c>
       <c r="I20" s="32"/>
     </row>
+    <row r="21" spans="1:13" s="82" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="82" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="82" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="83">
+        <v>46290</v>
+      </c>
+      <c r="F21" s="83">
+        <v>46311</v>
+      </c>
+      <c r="G21" s="82">
+        <f>F21-E21</f>
+        <v>21</v>
+      </c>
+      <c r="H21" s="82">
+        <v>12</v>
+      </c>
+      <c r="I21" s="82">
+        <f>J21/H21</f>
+        <v>0</v>
+      </c>
+    </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G23" s="18"/>
       <c r="H23" s="17"/>
@@ -3404,7 +3438,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21D6C99-536E-4F31-8A16-5ECA51AF8689}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" style="21" customWidth="1"/>
@@ -3426,7 +3460,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3981,15 +4015,15 @@
         <v>98</v>
       </c>
       <c r="F22" s="79">
-        <f t="shared" ref="F22" ca="1" si="0">TODAY()</f>
-        <v>46297</v>
+        <f ca="1">TODAY()</f>
+        <v>46317</v>
       </c>
       <c r="G22" s="77" t="e">
-        <f t="shared" ref="G22:G23" ca="1" si="1">F22-E22</f>
+        <f ca="1">F22-E22</f>
         <v>#VALUE!</v>
       </c>
       <c r="I22" s="77" t="e">
-        <f t="shared" ref="I22:I23" si="2">J22/H22</f>
+        <f>J22/H22</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4010,46 +4044,18 @@
         <v>46260</v>
       </c>
       <c r="G23" s="77">
-        <f t="shared" si="1"/>
+        <f>F23-E23</f>
         <v>23</v>
       </c>
       <c r="H23" s="77">
         <v>10</v>
       </c>
       <c r="I23" s="77">
-        <f t="shared" si="2"/>
+        <f>J23/H23</f>
         <v>0.6</v>
       </c>
       <c r="J23" s="77">
         <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" s="78" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="78" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="78" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="78" t="s">
-        <v>29</v>
-      </c>
-      <c r="E24" s="80">
-        <v>46290</v>
-      </c>
-      <c r="F24" s="80">
-        <v>46311</v>
-      </c>
-      <c r="G24" s="78">
-        <f>F24-E24</f>
-        <v>21</v>
-      </c>
-      <c r="H24" s="78">
-        <v>12</v>
-      </c>
-      <c r="I24" s="78">
-        <f>J24/H24</f>
-        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11" s="78" customFormat="1" x14ac:dyDescent="0.25">
@@ -4111,97 +4117,129 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="69"/>
-      <c r="C27" s="69"/>
-      <c r="D27" s="69"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="70"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="69"/>
-      <c r="J27" s="69"/>
-      <c r="K27" s="22"/>
-    </row>
-    <row r="28" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+    <row r="27" spans="1:11" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="78" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="78" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" s="78" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" s="80">
+        <v>46316</v>
+      </c>
+      <c r="F27" s="80">
+        <v>46337</v>
+      </c>
+      <c r="G27" s="78">
+        <f>F27-E27</f>
+        <v>21</v>
+      </c>
+      <c r="H27" s="78">
+        <v>12</v>
+      </c>
+      <c r="I27" s="78">
+        <f>J27/H27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E28" s="80"/>
+      <c r="F28" s="80"/>
+    </row>
+    <row r="29" spans="1:11" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E29" s="80"/>
+      <c r="F29" s="80"/>
+    </row>
+    <row r="30" spans="1:11" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E30" s="80"/>
+      <c r="F30" s="80"/>
+    </row>
+    <row r="31" spans="1:11" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E31" s="80"/>
+      <c r="F31" s="80"/>
+    </row>
+    <row r="32" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="B28" s="30" t="s">
+      <c r="B32" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="30" t="s">
+      <c r="C32" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="D28" s="31" t="s">
+      <c r="D32" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="E28" s="31">
+      <c r="E32" s="31">
         <v>45996</v>
       </c>
-      <c r="F28" s="31"/>
-      <c r="I28" s="32"/>
-    </row>
-    <row r="30" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="58"/>
-      <c r="B30" s="61" t="s">
+      <c r="F32" s="31"/>
+      <c r="I32" s="32"/>
+    </row>
+    <row r="34" spans="1:10" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="58"/>
+      <c r="B34" s="61" t="s">
         <v>80</v>
       </c>
-      <c r="C30" s="61" t="s">
+      <c r="C34" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="D30" s="61" t="s">
+      <c r="D34" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="E30" s="62">
+      <c r="E34" s="62">
         <v>46060</v>
       </c>
-      <c r="F30" s="62">
+      <c r="F34" s="62">
         <v>46081</v>
       </c>
-      <c r="G30" s="61">
-        <f>F30-E30</f>
+      <c r="G34" s="61">
+        <f>F34-E34</f>
         <v>21</v>
       </c>
-      <c r="H30" s="61">
+      <c r="H34" s="61">
         <v>12</v>
       </c>
-      <c r="I30" s="63">
-        <f>J30/H30</f>
+      <c r="I34" s="63">
+        <f>J34/H34</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="J30" s="61">
+      <c r="J34" s="61">
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:11" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="61" t="s">
+    <row r="35" spans="1:10" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="61" t="s">
+      <c r="C35" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="D31" s="61" t="s">
+      <c r="D35" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="E31" s="62">
+      <c r="E35" s="62">
         <v>46067</v>
       </c>
-      <c r="F31" s="62">
+      <c r="F35" s="62">
         <v>46088</v>
       </c>
-      <c r="G31" s="61">
-        <f>F31-E31</f>
+      <c r="G35" s="61">
+        <f>F35-E35</f>
         <v>21</v>
       </c>
-      <c r="H31" s="61">
+      <c r="H35" s="61">
         <v>12</v>
       </c>
-      <c r="I31" s="63">
-        <f>J31/H31</f>
+      <c r="I35" s="63">
+        <f>J35/H35</f>
         <v>0.41666666666666669</v>
       </c>
-      <c r="J31" s="61">
+      <c r="J35" s="61">
         <v>5</v>
       </c>
     </row>
@@ -4273,11 +4311,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>488</v>
+        <v>508</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -4305,11 +4343,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46297</v>
+        <v>46317</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>336</v>
+        <v>356</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7534A965-FF61-417D-AA4A-0DA497E9B255}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BF66F9-D7BA-41A3-8913-874979751B6D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="3" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
   <sheets>
     <sheet name="galinhas" sheetId="1" r:id="rId1"/>
     <sheet name="criando" sheetId="2" r:id="rId2"/>
     <sheet name="chocando" sheetId="3" r:id="rId3"/>
-    <sheet name="botando" sheetId="4" r:id="rId4"/>
+    <sheet name="Planilha1" sheetId="5" r:id="rId4"/>
+    <sheet name="botando" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="preçoDoOvo">galinhas!$H$1</definedName>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="110">
   <si>
     <t>HOJE</t>
   </si>
@@ -337,6 +338,30 @@
   </si>
   <si>
     <t>Sheila</t>
+  </si>
+  <si>
+    <t>frango</t>
+  </si>
+  <si>
+    <t>galinha</t>
+  </si>
+  <si>
+    <t>frangos</t>
+  </si>
+  <si>
+    <t>galo</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Cabeças</t>
+  </si>
+  <si>
+    <t>desconto 25%</t>
+  </si>
+  <si>
+    <t>TOTAL c/ descoto</t>
   </si>
 </sst>
 </file>
@@ -550,7 +575,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -800,6 +825,18 @@
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1137,7 +1174,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1414,11 +1451,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1521,18 +1558,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>2.7450980392156862E-2</v>
+        <v>2.7290448343079921E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
@@ -1632,18 +1669,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>3.4168564920273349E-2</v>
+        <v>3.3936651583710405E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1706,7 +1743,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-407</v>
+        <v>-410</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1741,7 +1778,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-407</v>
+        <v>-410</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1796,18 +1833,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>7.2639225181598066E-3</v>
+        <v>7.2115384615384619E-3</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1828,7 +1865,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1859,18 +1896,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>7.2639225181598066E-3</v>
+        <v>7.2115384615384619E-3</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1891,18 +1928,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>7.2639225181598066E-3</v>
+        <v>7.2115384615384619E-3</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2243,14 +2280,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2275,14 +2312,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2307,14 +2344,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2339,14 +2376,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2405,18 +2442,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H46" s="54">
         <f ca="1">F46*2</f>
-        <v>1016</v>
+        <v>1022</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2440,18 +2477,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H47" s="54">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2475,18 +2512,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>71</v>
       </c>
       <c r="H48" s="54">
         <f t="shared" ca="1" si="12"/>
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2558,14 +2595,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2723,7 +2760,7 @@
       <c r="C1" s="46"/>
       <c r="D1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="F1" s="46"/>
       <c r="G1" s="46"/>
@@ -2791,14 +2828,14 @@
       </c>
       <c r="F3" s="65">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="G3" s="65">
         <v>45947</v>
       </c>
       <c r="H3" s="64">
         <f t="shared" ref="H3:H8" ca="1" si="0">F3-G3</f>
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="I3" s="64" t="s">
         <v>54</v>
@@ -2832,14 +2869,14 @@
       </c>
       <c r="F4" s="65">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="G4" s="65">
         <v>45953</v>
       </c>
       <c r="H4" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="I4" s="64" t="s">
         <v>54</v>
@@ -2873,14 +2910,14 @@
       </c>
       <c r="F5" s="65">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="G5" s="65">
         <v>45956</v>
       </c>
       <c r="H5" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I5" s="64" t="s">
         <v>54</v>
@@ -2915,14 +2952,14 @@
       </c>
       <c r="F6" s="68">
         <f t="shared" ref="F6:F14" ca="1" si="2">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="G6" s="68">
         <v>45910</v>
       </c>
       <c r="H6" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="I6" s="67" t="s">
         <v>54</v>
@@ -2957,14 +2994,14 @@
       </c>
       <c r="F7" s="65">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="G7" s="65">
         <v>46027</v>
       </c>
       <c r="H7" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="I7" s="64" t="s">
         <v>54</v>
@@ -2998,14 +3035,14 @@
       </c>
       <c r="F8" s="72">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="G8" s="72">
         <v>46036</v>
       </c>
       <c r="H8" s="71">
         <f t="shared" ca="1" si="0"/>
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="I8" s="71" t="s">
         <v>54</v>
@@ -3039,14 +3076,14 @@
       </c>
       <c r="F9" s="72">
         <f t="shared" ca="1" si="2"/>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="G9" s="72">
         <v>46082</v>
       </c>
       <c r="H9" s="71">
         <f ca="1">F9-G9</f>
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="I9" s="71" t="s">
         <v>54</v>
@@ -3080,14 +3117,14 @@
       </c>
       <c r="F10" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="G10" s="18">
         <v>46089</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" ref="H10:H17" ca="1" si="3">F10-G10</f>
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>54</v>
@@ -3121,14 +3158,14 @@
       </c>
       <c r="F11" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="G11" s="70">
         <v>46129</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="I11" s="17" t="s">
         <v>54</v>
@@ -3156,14 +3193,14 @@
       </c>
       <c r="F12" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="G12" s="70">
         <v>46129</v>
       </c>
       <c r="H12" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>54</v>
@@ -3191,14 +3228,14 @@
       </c>
       <c r="F13" s="72">
         <f t="shared" ca="1" si="2"/>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="G13" s="72">
         <v>46182</v>
       </c>
       <c r="H13" s="71">
         <f t="shared" ca="1" si="3"/>
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="I13" s="71" t="s">
         <v>54</v>
@@ -3226,14 +3263,14 @@
       </c>
       <c r="F14" s="72">
         <f t="shared" ca="1" si="2"/>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="G14" s="72">
         <v>46184</v>
       </c>
       <c r="H14" s="71">
         <f t="shared" ca="1" si="3"/>
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I14" s="71" t="s">
         <v>54</v>
@@ -3261,14 +3298,14 @@
       </c>
       <c r="F15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="G15" s="18">
         <v>46216</v>
       </c>
       <c r="H15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I15" s="69" t="s">
         <v>54</v>
@@ -3296,11 +3333,11 @@
       </c>
       <c r="F16" s="72">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="G16" s="72">
         <f t="shared" ref="G16" ca="1" si="4">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="H16" s="71">
         <f t="shared" ca="1" si="3"/>
@@ -3332,14 +3369,14 @@
       </c>
       <c r="F17" s="18">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="G17" s="18">
         <v>46271</v>
       </c>
       <c r="H17" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I17" s="69" t="s">
         <v>54</v>
@@ -3460,7 +3497,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -4016,7 +4053,7 @@
       </c>
       <c r="F22" s="79">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="G22" s="77" t="e">
         <f ca="1">F22-E22</f>
@@ -4250,6 +4287,155 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6B6435F-C97E-4183-A722-401AF44A76BE}">
+  <dimension ref="A4:G15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="84"/>
+    <col min="3" max="3" width="9.140625" style="85"/>
+    <col min="4" max="4" width="11.5703125" style="84" customWidth="1"/>
+    <col min="5" max="6" width="9.140625" style="84"/>
+    <col min="7" max="7" width="13.42578125" style="84" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="84"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="84">
+        <v>1</v>
+      </c>
+      <c r="B4" s="84" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="85">
+        <v>50</v>
+      </c>
+      <c r="D4" s="85">
+        <f>C4*A4</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="84">
+        <v>1</v>
+      </c>
+      <c r="B5" s="84" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="85">
+        <v>50</v>
+      </c>
+      <c r="D5" s="85">
+        <f t="shared" ref="D5:D9" si="0">C5*A5</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="84">
+        <v>2</v>
+      </c>
+      <c r="B6" s="84" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="85">
+        <v>35</v>
+      </c>
+      <c r="D6" s="85">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="84">
+        <v>5</v>
+      </c>
+      <c r="B7" s="84" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="85">
+        <v>30</v>
+      </c>
+      <c r="D7" s="85">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="84">
+        <v>2</v>
+      </c>
+      <c r="B8" s="84" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="85">
+        <v>25</v>
+      </c>
+      <c r="D8" s="85">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="84">
+        <v>1</v>
+      </c>
+      <c r="B9" s="84" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="85">
+        <v>30</v>
+      </c>
+      <c r="D9" s="85">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C12" s="84"/>
+      <c r="F12" s="86" t="s">
+        <v>107</v>
+      </c>
+      <c r="G12" s="84">
+        <f>SUM(A:A)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C13" s="84"/>
+      <c r="F13" s="86" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="85">
+        <f>SUM(D:D)</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C14" s="84"/>
+      <c r="F14" s="87" t="s">
+        <v>108</v>
+      </c>
+      <c r="G14" s="85">
+        <f>G13/4</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C15" s="84"/>
+      <c r="F15" s="87" t="s">
+        <v>109</v>
+      </c>
+      <c r="G15" s="85">
+        <f>G13-G14</f>
+        <v>300</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC1ACAAB-4C7C-47DD-B348-5E0B06D77598}">
   <dimension ref="A1:J7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4311,11 +4497,11 @@
       </c>
       <c r="E2" s="20">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="F2" s="19">
         <f ca="1">E2-D2</f>
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G2" s="19" t="s">
         <v>71</v>
@@ -4343,11 +4529,11 @@
       </c>
       <c r="E3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46320</v>
       </c>
       <c r="F3" s="19">
         <f ca="1">E3-D3</f>
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="G3" s="19" t="s">
         <v>71</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BF66F9-D7BA-41A3-8913-874979751B6D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81C0C7E-BFDE-4849-93D5-5AA691D758B3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="3" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="111">
   <si>
     <t>HOJE</t>
   </si>
@@ -362,6 +362,9 @@
   </si>
   <si>
     <t>TOTAL c/ descoto</t>
+  </si>
+  <si>
+    <t>Valor combinado</t>
   </si>
 </sst>
 </file>
@@ -4288,7 +4291,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6B6435F-C97E-4183-A722-401AF44A76BE}">
-  <dimension ref="A4:G15"/>
+  <dimension ref="A4:G16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="84"/>
@@ -4427,6 +4430,14 @@
       <c r="G15" s="85">
         <f>G13-G14</f>
         <v>300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F16" s="87" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16" s="85">
+        <v>250</v>
       </c>
     </row>
   </sheetData>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81C0C7E-BFDE-4849-93D5-5AA691D758B3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D21655-9B1D-43D0-8E49-C6CBA4732534}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="3" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="1" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
   <sheets>
     <sheet name="galinhas" sheetId="1" r:id="rId1"/>
     <sheet name="criando" sheetId="2" r:id="rId2"/>
     <sheet name="chocando" sheetId="3" r:id="rId3"/>
-    <sheet name="Planilha1" sheetId="5" r:id="rId4"/>
-    <sheet name="botando" sheetId="4" r:id="rId5"/>
+    <sheet name="Martinho" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="preçoDoOvo">galinhas!$H$1</definedName>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="107">
   <si>
     <t>HOJE</t>
   </si>
@@ -229,9 +228,6 @@
     <t>unidade</t>
   </si>
   <si>
-    <t>quantidade</t>
-  </si>
-  <si>
     <t>tipo</t>
   </si>
   <si>
@@ -257,15 +253,6 @@
   </si>
   <si>
     <t>preço do ovo</t>
-  </si>
-  <si>
-    <t>iniciais</t>
-  </si>
-  <si>
-    <t>início</t>
-  </si>
-  <si>
-    <t>ovosXdia</t>
   </si>
   <si>
     <t>polaca</t>
@@ -374,7 +361,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -487,8 +474,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -498,6 +492,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,7 +578,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -823,12 +823,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -840,6 +834,39 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1177,7 +1204,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1187,7 +1214,7 @@
         <v>58</v>
       </c>
       <c r="G1" s="53" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H1" s="54">
         <v>2</v>
@@ -1454,11 +1481,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1561,18 +1588,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>2.7290448343079921E-2</v>
+        <v>2.7184466019417475E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
@@ -1672,18 +1699,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>3.3936651583710405E-2</v>
+        <v>3.3783783783783786E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1746,7 +1773,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-410</v>
+        <v>-412</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1781,7 +1808,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-410</v>
+        <v>-412</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1836,18 +1863,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>7.2115384615384619E-3</v>
+        <v>7.1770334928229667E-3</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1868,7 +1895,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1899,18 +1926,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>7.2115384615384619E-3</v>
+        <v>7.1770334928229667E-3</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1931,18 +1958,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>7.2115384615384619E-3</v>
+        <v>7.1770334928229667E-3</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2283,14 +2310,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2315,14 +2342,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2347,14 +2374,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2379,14 +2406,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2445,18 +2472,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H46" s="54">
         <f ca="1">F46*2</f>
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2480,18 +2507,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H47" s="54">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2515,18 +2542,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H48" s="54">
         <f t="shared" ca="1" si="12"/>
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2598,14 +2625,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2662,7 +2689,7 @@
     </row>
     <row r="55" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="30" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B55" s="30" t="s">
         <v>31</v>
@@ -2671,7 +2698,7 @@
         <v>42</v>
       </c>
       <c r="D55" s="31" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E55" s="31">
         <v>45996</v>
@@ -2698,7 +2725,7 @@
     </row>
     <row r="57" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="30" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B57" s="30" t="s">
         <v>24</v>
@@ -2717,7 +2744,7 @@
     </row>
     <row r="58" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="30" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B58" s="30" t="s">
         <v>31</v>
@@ -2742,7 +2769,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B0995D-FE85-4EC0-91CA-7B21E8F79AC2}">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="10.7109375" style="47"/>
@@ -2763,7 +2790,7 @@
       <c r="C1" s="46"/>
       <c r="D1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="F1" s="46"/>
       <c r="G1" s="46"/>
@@ -2772,7 +2799,7 @@
         <v>13</v>
       </c>
       <c r="I1" s="49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J1" s="57"/>
       <c r="K1" s="57"/>
@@ -2786,10 +2813,10 @@
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="51" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E2" s="50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F2" s="51" t="s">
         <v>61</v>
@@ -2804,13 +2831,13 @@
         <v>64</v>
       </c>
       <c r="J2" s="50" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K2" s="50" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L2" s="76" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="64" customFormat="1" x14ac:dyDescent="0.25">
@@ -2831,14 +2858,14 @@
       </c>
       <c r="F3" s="65">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="G3" s="65">
         <v>45947</v>
       </c>
       <c r="H3" s="64">
         <f t="shared" ref="H3:H8" ca="1" si="0">F3-G3</f>
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I3" s="64" t="s">
         <v>54</v>
@@ -2872,14 +2899,14 @@
       </c>
       <c r="F4" s="65">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="G4" s="65">
         <v>45953</v>
       </c>
       <c r="H4" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="I4" s="64" t="s">
         <v>54</v>
@@ -2913,14 +2940,14 @@
       </c>
       <c r="F5" s="65">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="G5" s="65">
         <v>45956</v>
       </c>
       <c r="H5" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="I5" s="64" t="s">
         <v>54</v>
@@ -2955,14 +2982,14 @@
       </c>
       <c r="F6" s="68">
         <f t="shared" ref="F6:F14" ca="1" si="2">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="G6" s="68">
         <v>45910</v>
       </c>
       <c r="H6" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I6" s="67" t="s">
         <v>54</v>
@@ -2997,14 +3024,14 @@
       </c>
       <c r="F7" s="65">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="G7" s="65">
         <v>46027</v>
       </c>
       <c r="H7" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="I7" s="64" t="s">
         <v>54</v>
@@ -3038,14 +3065,14 @@
       </c>
       <c r="F8" s="72">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="G8" s="72">
         <v>46036</v>
       </c>
       <c r="H8" s="71">
         <f t="shared" ca="1" si="0"/>
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="I8" s="71" t="s">
         <v>54</v>
@@ -3066,27 +3093,27 @@
         <v>18</v>
       </c>
       <c r="B9" s="71" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C9" s="71" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D9" s="71" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E9" s="71" t="s">
         <v>29</v>
       </c>
       <c r="F9" s="72">
         <f t="shared" ca="1" si="2"/>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="G9" s="72">
         <v>46082</v>
       </c>
       <c r="H9" s="71">
         <f ca="1">F9-G9</f>
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I9" s="71" t="s">
         <v>54</v>
@@ -3120,14 +3147,14 @@
       </c>
       <c r="F10" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="G10" s="18">
         <v>46089</v>
       </c>
       <c r="H10" s="17">
         <f t="shared" ref="H10:H17" ca="1" si="3">F10-G10</f>
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>54</v>
@@ -3161,14 +3188,14 @@
       </c>
       <c r="F11" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="G11" s="70">
         <v>46129</v>
       </c>
       <c r="H11" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I11" s="17" t="s">
         <v>54</v>
@@ -3186,24 +3213,24 @@
     </row>
     <row r="12" spans="1:13" s="69" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C12" s="69" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D12" s="69" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E12" s="69" t="s">
         <v>34</v>
       </c>
       <c r="F12" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="G12" s="70">
         <v>46129</v>
       </c>
       <c r="H12" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>54</v>
@@ -3221,24 +3248,24 @@
     </row>
     <row r="13" spans="1:13" s="71" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C13" s="71" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D13" s="71" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E13" s="71" t="s">
         <v>29</v>
       </c>
       <c r="F13" s="72">
         <f t="shared" ca="1" si="2"/>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="G13" s="72">
         <v>46182</v>
       </c>
       <c r="H13" s="71">
         <f t="shared" ca="1" si="3"/>
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I13" s="71" t="s">
         <v>54</v>
@@ -3256,24 +3283,24 @@
     </row>
     <row r="14" spans="1:13" s="71" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C14" s="71" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D14" s="71" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E14" s="71" t="s">
         <v>34</v>
       </c>
       <c r="F14" s="72">
         <f t="shared" ca="1" si="2"/>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="G14" s="72">
         <v>46184</v>
       </c>
       <c r="H14" s="71">
         <f t="shared" ca="1" si="3"/>
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I14" s="71" t="s">
         <v>54</v>
@@ -3291,24 +3318,24 @@
     </row>
     <row r="15" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C15" s="17" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>34</v>
       </c>
       <c r="F15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="G15" s="18">
         <v>46216</v>
       </c>
       <c r="H15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I15" s="69" t="s">
         <v>54</v>
@@ -3326,21 +3353,21 @@
     </row>
     <row r="16" spans="1:13" s="71" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C16" s="71" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D16" s="71" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E16" s="71" t="s">
         <v>29</v>
       </c>
       <c r="F16" s="72">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="G16" s="72">
         <f t="shared" ref="G16" ca="1" si="4">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="H16" s="71">
         <f t="shared" ca="1" si="3"/>
@@ -3362,24 +3389,24 @@
     </row>
     <row r="17" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C17" s="17" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>29</v>
       </c>
       <c r="F17" s="18">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="G17" s="18">
         <v>46271</v>
       </c>
       <c r="H17" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I17" s="69" t="s">
         <v>54</v>
@@ -3401,7 +3428,10 @@
       <c r="I18" s="69"/>
       <c r="J18" s="69"/>
       <c r="K18" s="69"/>
-      <c r="L18" s="22"/>
+      <c r="L18" s="22" t="e">
+        <f t="shared" ref="L18:L23" si="5">K18/J18</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="19" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C19" s="73"/>
@@ -3413,7 +3443,10 @@
       <c r="I19" s="69"/>
       <c r="J19" s="69"/>
       <c r="K19" s="69"/>
-      <c r="L19" s="22"/>
+      <c r="L19" s="22" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="M19" s="17"/>
     </row>
     <row r="20" spans="1:13" s="30" customFormat="1" x14ac:dyDescent="0.25">
@@ -3433,42 +3466,128 @@
         <v>45997</v>
       </c>
       <c r="I20" s="32"/>
-    </row>
-    <row r="21" spans="1:13" s="82" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="82" t="s">
+      <c r="L20" s="91" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" s="92" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="82" t="s">
+      <c r="C21" s="92" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="82" t="s">
+      <c r="E21" s="92" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="83">
-        <v>46290</v>
-      </c>
-      <c r="F21" s="83">
+      <c r="F21" s="93">
+        <f ca="1">TODAY()</f>
+        <v>46322</v>
+      </c>
+      <c r="G21" s="93">
         <v>46311</v>
       </c>
-      <c r="G21" s="82">
-        <f>F21-E21</f>
-        <v>21</v>
-      </c>
-      <c r="H21" s="82">
+      <c r="H21" s="92">
         <v>12</v>
       </c>
-      <c r="I21" s="82">
-        <f>J21/H21</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="G23" s="18"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="23"/>
+      <c r="I21" s="92" t="s">
+        <v>54</v>
+      </c>
+      <c r="J21" s="92">
+        <v>1</v>
+      </c>
+      <c r="K21" s="92">
+        <v>1</v>
+      </c>
+      <c r="L21" s="94">
+        <f>K21/J21</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" s="92" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="92" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="92" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" s="92" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="92" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="92" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22" s="93">
+        <f t="shared" ref="F22:F23" ca="1" si="6">TODAY()</f>
+        <v>46322</v>
+      </c>
+      <c r="G22" s="93">
+        <v>46322</v>
+      </c>
+      <c r="H22" s="92">
+        <v>12</v>
+      </c>
+      <c r="I22" s="92" t="s">
+        <v>54</v>
+      </c>
+      <c r="J22" s="92">
+        <v>8</v>
+      </c>
+      <c r="K22" s="92">
+        <v>8</v>
+      </c>
+      <c r="L22" s="94">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" s="92" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="92" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="92" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" s="92" t="s">
+        <v>97</v>
+      </c>
+      <c r="E23" s="92" t="s">
+        <v>29</v>
+      </c>
+      <c r="F23" s="93">
+        <f t="shared" ca="1" si="6"/>
+        <v>46322</v>
+      </c>
+      <c r="G23" s="93">
+        <v>46322</v>
+      </c>
+      <c r="H23" s="92">
+        <v>12</v>
+      </c>
+      <c r="I23" s="92" t="s">
+        <v>54</v>
+      </c>
+      <c r="J23" s="92">
+        <v>1</v>
+      </c>
+      <c r="K23" s="92">
+        <v>1</v>
+      </c>
+      <c r="L23" s="94">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" s="95" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F24" s="96"/>
+      <c r="G24" s="96"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -3489,7 +3608,7 @@
     <col min="6" max="6" width="16.85546875" style="81" customWidth="1"/>
     <col min="7" max="7" width="13" style="21" customWidth="1"/>
     <col min="8" max="8" width="15.140625" style="21" customWidth="1"/>
-    <col min="9" max="9" width="15.28515625" style="21" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" style="90" customWidth="1"/>
     <col min="10" max="10" width="11.7109375" style="21" customWidth="1"/>
     <col min="11" max="16384" width="9.140625" style="21"/>
   </cols>
@@ -3500,7 +3619,7 @@
       </c>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -3509,8 +3628,9 @@
         <v>#REF!</v>
       </c>
       <c r="H1" s="49" t="s">
-        <v>73</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="I1" s="52"/>
     </row>
     <row r="2" spans="1:10" s="55" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
@@ -3520,28 +3640,28 @@
         <v>60</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D2" s="55" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F2" s="56" t="s">
         <v>62</v>
       </c>
       <c r="G2" s="55" t="s">
+        <v>69</v>
+      </c>
+      <c r="H2" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="55" t="s">
+      <c r="I2" s="87" t="s">
         <v>71</v>
       </c>
-      <c r="I2" s="55" t="s">
-        <v>72</v>
-      </c>
       <c r="J2" s="55" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="58" customFormat="1" x14ac:dyDescent="0.25">
@@ -3589,7 +3709,7 @@
         <v>42</v>
       </c>
       <c r="D4" s="58" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E4" s="59">
         <v>45982</v>
@@ -3677,6 +3797,7 @@
     <row r="7" spans="1:10" s="61" customFormat="1" x14ac:dyDescent="0.25">
       <c r="E7" s="62"/>
       <c r="F7" s="62"/>
+      <c r="I7" s="63"/>
     </row>
     <row r="9" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="64" t="s">
@@ -3717,10 +3838,10 @@
         <v>17</v>
       </c>
       <c r="B10" s="64" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C10" s="64" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D10" s="64" t="s">
         <v>34</v>
@@ -3751,10 +3872,10 @@
         <v>17</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D11" s="64" t="s">
         <v>29</v>
@@ -3821,10 +3942,10 @@
     </row>
     <row r="14" spans="1:10" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="77" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C14" s="77" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D14" s="77" t="s">
         <v>29</v>
@@ -3842,7 +3963,7 @@
       <c r="H14" s="77">
         <v>12</v>
       </c>
-      <c r="I14" s="77">
+      <c r="I14" s="88">
         <f>J14/H14</f>
         <v>0.33333333333333331</v>
       </c>
@@ -3852,10 +3973,10 @@
     </row>
     <row r="15" spans="1:10" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="77" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C15" s="77" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D15" s="77" t="s">
         <v>34</v>
@@ -3873,16 +3994,16 @@
       <c r="H15" s="77">
         <v>12</v>
       </c>
-      <c r="I15" s="77" t="s">
-        <v>92</v>
+      <c r="I15" s="88" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="77" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C16" s="77" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D16" s="77" t="s">
         <v>34</v>
@@ -3900,7 +4021,7 @@
       <c r="H16" s="77">
         <v>3</v>
       </c>
-      <c r="I16" s="77">
+      <c r="I16" s="88">
         <f>J16/H16</f>
         <v>0.33333333333333331</v>
       </c>
@@ -3928,7 +4049,7 @@
       <c r="H17" s="77">
         <v>12</v>
       </c>
-      <c r="I17" s="77">
+      <c r="I17" s="88">
         <f>J17/H17</f>
         <v>1</v>
       </c>
@@ -3942,10 +4063,10 @@
         <v>18</v>
       </c>
       <c r="B18" s="77" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C18" s="77" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D18" s="77" t="s">
         <v>34</v>
@@ -3963,7 +4084,7 @@
       <c r="H18" s="77">
         <v>12</v>
       </c>
-      <c r="I18" s="77">
+      <c r="I18" s="88">
         <f>J18/H18</f>
         <v>0.66666666666666663</v>
       </c>
@@ -3978,6 +4099,7 @@
       <c r="B19" s="77" t="s">
         <v>7</v>
       </c>
+      <c r="I19" s="88"/>
     </row>
     <row r="20" spans="1:11" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="77" t="s">
@@ -3996,14 +4118,14 @@
         <v>46245</v>
       </c>
       <c r="G20" s="77">
-        <f>F20-E20</f>
+        <f t="shared" ref="G20:G25" si="0">F20-E20</f>
         <v>24</v>
       </c>
       <c r="H20" s="77">
         <v>12</v>
       </c>
-      <c r="I20" s="77">
-        <f>J20/H20</f>
+      <c r="I20" s="88">
+        <f t="shared" ref="I20:I25" si="1">J20/H20</f>
         <v>0.91666666666666663</v>
       </c>
       <c r="J20" s="77">
@@ -4027,14 +4149,14 @@
         <v>46245</v>
       </c>
       <c r="G21" s="77">
-        <f>F21-E21</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="H21" s="77">
         <v>12</v>
       </c>
-      <c r="I21" s="77">
-        <f>J21/H21</f>
+      <c r="I21" s="88">
+        <f t="shared" si="1"/>
         <v>0.58333333333333337</v>
       </c>
       <c r="J21" s="77">
@@ -4043,36 +4165,36 @@
     </row>
     <row r="22" spans="1:11" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="77" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C22" s="77" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D22" s="77" t="s">
         <v>34</v>
       </c>
       <c r="E22" s="79" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F22" s="79">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46322</v>
       </c>
       <c r="G22" s="77" t="e">
-        <f ca="1">F22-E22</f>
+        <f t="shared" ca="1" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="I22" s="77" t="e">
-        <f>J22/H22</f>
+      <c r="I22" s="88" t="e">
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="23" spans="1:11" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="77" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C23" s="77" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D23" s="77" t="s">
         <v>29</v>
@@ -4084,85 +4206,88 @@
         <v>46260</v>
       </c>
       <c r="G23" s="77">
-        <f>F23-E23</f>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="H23" s="77">
         <v>10</v>
       </c>
-      <c r="I23" s="77">
-        <f>J23/H23</f>
+      <c r="I23" s="88">
+        <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
       <c r="J23" s="77">
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:11" s="78" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="78" t="s">
-        <v>100</v>
-      </c>
-      <c r="C25" s="78" t="s">
-        <v>101</v>
-      </c>
-      <c r="D25" s="78" t="s">
+    <row r="24" spans="1:11" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="77" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" s="77" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" s="77" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="79">
+        <v>46297</v>
+      </c>
+      <c r="F24" s="79">
+        <v>46318</v>
+      </c>
+      <c r="G24" s="77">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="H24" s="77">
+        <v>12</v>
+      </c>
+      <c r="I24" s="88">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J24" s="77">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="77" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" s="77" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="80">
+      <c r="E25" s="79">
         <v>46291</v>
       </c>
-      <c r="F25" s="80">
+      <c r="F25" s="79">
         <v>46312</v>
       </c>
-      <c r="G25" s="78">
-        <f>F25-E25</f>
+      <c r="G25" s="77">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="H25" s="78">
+      <c r="H25" s="77">
         <v>12</v>
       </c>
-      <c r="I25" s="78">
-        <f>J25/H25</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" s="78" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="78" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" s="78" t="s">
-        <v>95</v>
-      </c>
-      <c r="C26" s="78" t="s">
-        <v>94</v>
-      </c>
-      <c r="D26" s="78" t="s">
-        <v>34</v>
-      </c>
-      <c r="E26" s="80">
-        <v>46297</v>
-      </c>
-      <c r="F26" s="80">
-        <v>46318</v>
-      </c>
-      <c r="G26" s="78">
-        <f>F26-E26</f>
-        <v>21</v>
-      </c>
-      <c r="H26" s="78">
-        <v>12</v>
-      </c>
-      <c r="I26" s="78">
-        <f>J26/H26</f>
+      <c r="I25" s="88">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11" s="78" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="78" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C27" s="78" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D27" s="78" t="s">
         <v>29</v>
@@ -4180,30 +4305,29 @@
       <c r="H27" s="78">
         <v>12</v>
       </c>
-      <c r="I27" s="78">
+      <c r="I27" s="89">
         <f>J27/H27</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" s="78" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="E28" s="80"/>
-      <c r="F28" s="80"/>
     </row>
     <row r="29" spans="1:11" s="78" customFormat="1" x14ac:dyDescent="0.25">
       <c r="E29" s="80"/>
       <c r="F29" s="80"/>
+      <c r="I29" s="89"/>
     </row>
     <row r="30" spans="1:11" s="78" customFormat="1" x14ac:dyDescent="0.25">
       <c r="E30" s="80"/>
       <c r="F30" s="80"/>
+      <c r="I30" s="89"/>
     </row>
     <row r="31" spans="1:11" s="78" customFormat="1" x14ac:dyDescent="0.25">
       <c r="E31" s="80"/>
       <c r="F31" s="80"/>
+      <c r="I31" s="89"/>
     </row>
     <row r="32" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="30" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B32" s="30" t="s">
         <v>31</v>
@@ -4212,7 +4336,7 @@
         <v>42</v>
       </c>
       <c r="D32" s="31" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E32" s="31">
         <v>45996</v>
@@ -4223,10 +4347,10 @@
     <row r="34" spans="1:10" s="61" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="58"/>
       <c r="B34" s="61" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C34" s="61" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D34" s="61" t="s">
         <v>29</v>
@@ -4291,292 +4415,161 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6B6435F-C97E-4183-A722-401AF44A76BE}">
-  <dimension ref="A4:G16"/>
+  <dimension ref="A2:H15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="84"/>
-    <col min="3" max="3" width="9.140625" style="85"/>
-    <col min="4" max="4" width="11.5703125" style="84" customWidth="1"/>
-    <col min="5" max="6" width="9.140625" style="84"/>
-    <col min="7" max="7" width="13.42578125" style="84" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="84"/>
+    <col min="1" max="1" width="10.7109375" style="82" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="82"/>
+    <col min="3" max="3" width="9.140625" style="83"/>
+    <col min="4" max="4" width="11.5703125" style="82" customWidth="1"/>
+    <col min="5" max="6" width="9.140625" style="82"/>
+    <col min="7" max="7" width="13.42578125" style="82" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="82"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="84">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="86">
+        <v>46319</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="82">
         <v>1</v>
       </c>
-      <c r="B4" s="84" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" s="85">
+      <c r="B4" s="82" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="83">
         <v>50</v>
       </c>
-      <c r="D4" s="85">
+      <c r="D4" s="83">
         <f>C4*A4</f>
         <v>50</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="84">
+      <c r="G4" s="84" t="s">
+        <v>103</v>
+      </c>
+      <c r="H4" s="82">
+        <f>SUM(A:A)</f>
+        <v>46331</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="82">
         <v>1</v>
       </c>
-      <c r="B5" s="84" t="s">
-        <v>103</v>
-      </c>
-      <c r="C5" s="85">
+      <c r="B5" s="82" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="83">
         <v>50</v>
       </c>
-      <c r="D5" s="85">
+      <c r="D5" s="83">
         <f t="shared" ref="D5:D9" si="0">C5*A5</f>
         <v>50</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="84">
+      <c r="G5" s="84" t="s">
+        <v>102</v>
+      </c>
+      <c r="H5" s="83">
+        <f>SUM(D:D)</f>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="82">
         <v>2</v>
       </c>
-      <c r="B6" s="84" t="s">
-        <v>104</v>
-      </c>
-      <c r="C6" s="85">
+      <c r="B6" s="82" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="83">
         <v>35</v>
       </c>
-      <c r="D6" s="85">
+      <c r="D6" s="83">
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="84">
+      <c r="G6" s="85" t="s">
+        <v>104</v>
+      </c>
+      <c r="H6" s="83">
+        <f>H5/4</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="82">
         <v>5</v>
       </c>
-      <c r="B7" s="84" t="s">
-        <v>104</v>
-      </c>
-      <c r="C7" s="85">
+      <c r="B7" s="82" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="83">
         <v>30</v>
       </c>
-      <c r="D7" s="85">
+      <c r="D7" s="83">
         <f t="shared" si="0"/>
         <v>150</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="84">
+      <c r="G7" s="85" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="83">
+        <f>H5-H6</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="82">
         <v>2</v>
       </c>
-      <c r="B8" s="84" t="s">
-        <v>104</v>
-      </c>
-      <c r="C8" s="85">
+      <c r="B8" s="82" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="83">
         <v>25</v>
       </c>
-      <c r="D8" s="85">
+      <c r="D8" s="83">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="84">
+      <c r="G8" s="85" t="s">
+        <v>106</v>
+      </c>
+      <c r="H8" s="83">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="82">
         <v>1</v>
       </c>
-      <c r="B9" s="84" t="s">
-        <v>105</v>
-      </c>
-      <c r="C9" s="85">
+      <c r="B9" s="82" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="83">
         <v>30</v>
       </c>
-      <c r="D9" s="85">
+      <c r="D9" s="83">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C12" s="84"/>
-      <c r="F12" s="86" t="s">
-        <v>107</v>
-      </c>
-      <c r="G12" s="84">
-        <f>SUM(A:A)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C13" s="84"/>
-      <c r="F13" s="86" t="s">
-        <v>106</v>
-      </c>
-      <c r="G13" s="85">
-        <f>SUM(D:D)</f>
-        <v>400</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C14" s="84"/>
-      <c r="F14" s="87" t="s">
-        <v>108</v>
-      </c>
-      <c r="G14" s="85">
-        <f>G13/4</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C15" s="84"/>
-      <c r="F15" s="87" t="s">
-        <v>109</v>
-      </c>
-      <c r="G15" s="85">
-        <f>G13-G14</f>
-        <v>300</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F16" s="87" t="s">
-        <v>110</v>
-      </c>
-      <c r="G16" s="85">
-        <v>250</v>
-      </c>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C12" s="82"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C13" s="82"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C14" s="82"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C15" s="82"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC1ACAAB-4C7C-47DD-B348-5E0B06D77598}">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="1"/>
-    <col min="3" max="3" width="16.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="1"/>
-    <col min="8" max="8" width="9.140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J1" s="1">
-        <f>SUM(I:I)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="20">
-        <v>45809</v>
-      </c>
-      <c r="E2" s="20">
-        <f ca="1">TODAY()</f>
-        <v>46320</v>
-      </c>
-      <c r="F2" s="19">
-        <f ca="1">E2-D2</f>
-        <v>511</v>
-      </c>
-      <c r="G2" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="H2" s="54"/>
-      <c r="I2" s="19">
-        <v>1</v>
-      </c>
-      <c r="J2" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="20">
-        <v>45961</v>
-      </c>
-      <c r="E3" s="20">
-        <f ca="1">TODAY()</f>
-        <v>46320</v>
-      </c>
-      <c r="F3" s="19">
-        <f ca="1">E3-D3</f>
-        <v>359</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="H3" s="54"/>
-      <c r="I3" s="19">
-        <v>1</v>
-      </c>
-      <c r="J3" s="19" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="30" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="31">
-        <v>45997</v>
-      </c>
-      <c r="E7" s="31"/>
-      <c r="H7" s="32"/>
-      <c r="J7" s="30" t="s">
-        <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-</worksheet>
 </file>
--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D21655-9B1D-43D0-8E49-C6CBA4732534}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A322C0-4BCF-4D1A-9BC4-CF383366B752}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="1" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
   <sheets>
     <sheet name="galinhas" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="106">
   <si>
     <t>HOJE</t>
   </si>
@@ -208,9 +208,6 @@
   </si>
   <si>
     <t>cabeças</t>
-  </si>
-  <si>
-    <t>estado</t>
   </si>
   <si>
     <t>sigla</t>
@@ -1204,7 +1201,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1214,7 +1211,7 @@
         <v>58</v>
       </c>
       <c r="G1" s="53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H1" s="54">
         <v>2</v>
@@ -1481,11 +1478,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1588,18 +1585,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>2.7184466019417475E-2</v>
+        <v>2.7131782945736434E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
@@ -1699,18 +1696,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>3.3783783783783786E-2</v>
+        <v>3.3707865168539325E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1773,7 +1770,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-412</v>
+        <v>-413</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1808,7 +1805,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-412</v>
+        <v>-413</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1863,18 +1860,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>7.1770334928229667E-3</v>
+        <v>7.1599045346062056E-3</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1895,7 +1892,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1926,18 +1923,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>7.1770334928229667E-3</v>
+        <v>7.1599045346062056E-3</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1958,18 +1955,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>7.1770334928229667E-3</v>
+        <v>7.1599045346062056E-3</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2310,14 +2307,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2342,14 +2339,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2374,14 +2371,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2406,14 +2403,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2472,18 +2469,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G46" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H46" s="54">
         <f ca="1">F46*2</f>
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2507,18 +2504,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H47" s="54">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2542,18 +2539,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H48" s="54">
         <f t="shared" ca="1" si="12"/>
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2625,14 +2622,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2689,7 +2686,7 @@
     </row>
     <row r="55" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B55" s="30" t="s">
         <v>31</v>
@@ -2698,7 +2695,7 @@
         <v>42</v>
       </c>
       <c r="D55" s="31" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E55" s="31">
         <v>45996</v>
@@ -2725,7 +2722,7 @@
     </row>
     <row r="57" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B57" s="30" t="s">
         <v>24</v>
@@ -2744,7 +2741,7 @@
     </row>
     <row r="58" spans="1:10" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B58" s="30" t="s">
         <v>31</v>
@@ -2769,825 +2766,789 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B0995D-FE85-4EC0-91CA-7B21E8F79AC2}">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="10.7109375" style="47"/>
-    <col min="4" max="4" width="17.42578125" style="47" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" style="47"/>
-    <col min="6" max="6" width="10.7109375" style="48"/>
-    <col min="7" max="7" width="14.7109375" style="48" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" style="47"/>
-    <col min="9" max="9" width="15.140625" style="47" customWidth="1"/>
-    <col min="10" max="10" width="13.85546875" style="47" customWidth="1"/>
-    <col min="11" max="16384" width="10.7109375" style="47"/>
+    <col min="1" max="2" width="10.7109375" style="47"/>
+    <col min="3" max="3" width="17.42578125" style="47" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" style="47"/>
+    <col min="5" max="5" width="10.7109375" style="48"/>
+    <col min="6" max="6" width="14.7109375" style="48" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" style="47"/>
+    <col min="8" max="8" width="15.140625" style="47" customWidth="1"/>
+    <col min="9" max="9" width="13.85546875" style="47" customWidth="1"/>
+    <col min="10" max="16384" width="10.7109375" style="47"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="49" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B1" s="46" t="s">
+    <row r="1" spans="1:12" s="49" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46">
+      <c r="B1" s="46"/>
+      <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
-      </c>
+        <v>46323</v>
+      </c>
+      <c r="E1" s="46"/>
       <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="49">
-        <f>SUM(K7:K10)</f>
+      <c r="G1" s="49">
+        <f>SUM(J7:J10)</f>
         <v>13</v>
       </c>
-      <c r="I1" s="49" t="s">
-        <v>67</v>
-      </c>
+      <c r="H1" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="57"/>
       <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-    </row>
-    <row r="2" spans="1:13" s="50" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="50" t="s">
+    </row>
+    <row r="2" spans="1:12" s="50" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="51"/>
+      <c r="C2" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="51" t="s">
         <v>60</v>
-      </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="50" t="s">
-        <v>65</v>
       </c>
       <c r="F2" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="50" t="s">
         <v>62</v>
       </c>
       <c r="H2" s="50" t="s">
         <v>63</v>
       </c>
       <c r="I2" s="50" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="J2" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="K2" s="50" t="s">
-        <v>79</v>
-      </c>
-      <c r="L2" s="76" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" s="64" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K2" s="76" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="64" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="64" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B3" s="64" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D3" s="64" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="64" t="s">
         <v>29</v>
       </c>
+      <c r="E3" s="65">
+        <f ca="1">TODAY()</f>
+        <v>46323</v>
+      </c>
       <c r="F3" s="65">
-        <f ca="1">TODAY()</f>
-        <v>46322</v>
-      </c>
-      <c r="G3" s="65">
         <v>45947</v>
       </c>
-      <c r="H3" s="64">
-        <f t="shared" ref="H3:H8" ca="1" si="0">F3-G3</f>
-        <v>375</v>
-      </c>
-      <c r="I3" s="64" t="s">
+      <c r="G3" s="64">
+        <f t="shared" ref="G3:G8" ca="1" si="0">E3-F3</f>
+        <v>376</v>
+      </c>
+      <c r="H3" s="64" t="s">
         <v>54</v>
       </c>
+      <c r="I3" s="64">
+        <v>4</v>
+      </c>
       <c r="J3" s="64">
-        <v>4</v>
-      </c>
-      <c r="K3" s="64">
         <v>0</v>
       </c>
-      <c r="L3" s="66">
-        <f>K3/J3</f>
+      <c r="K3" s="66">
+        <f>J3/I3</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="64" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" s="64" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="64" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="B4" s="64" t="s">
         <v>57</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D4" s="64" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="64" t="s">
         <v>34</v>
       </c>
+      <c r="E4" s="65">
+        <f ca="1">TODAY()</f>
+        <v>46323</v>
+      </c>
       <c r="F4" s="65">
-        <f ca="1">TODAY()</f>
-        <v>46322</v>
-      </c>
-      <c r="G4" s="65">
         <v>45953</v>
       </c>
-      <c r="H4" s="64">
+      <c r="G4" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>369</v>
-      </c>
-      <c r="I4" s="64" t="s">
+        <v>370</v>
+      </c>
+      <c r="H4" s="64" t="s">
         <v>54</v>
       </c>
+      <c r="I4" s="64">
+        <v>8</v>
+      </c>
       <c r="J4" s="64">
-        <v>8</v>
-      </c>
-      <c r="K4" s="64">
         <v>0</v>
       </c>
-      <c r="L4" s="66">
-        <f t="shared" ref="L4:L14" si="1">K4/J4</f>
+      <c r="K4" s="66">
+        <f t="shared" ref="K4:K14" si="1">J4/I4</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="64" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" s="64" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="64" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B5" s="64" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" s="64" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="65">
+        <f ca="1">TODAY()</f>
+        <v>46323</v>
+      </c>
+      <c r="F5" s="65">
+        <v>45956</v>
+      </c>
+      <c r="G5" s="64">
+        <f t="shared" ca="1" si="0"/>
+        <v>367</v>
+      </c>
+      <c r="H5" s="64" t="s">
+        <v>54</v>
+      </c>
+      <c r="I5" s="64">
         <v>8</v>
       </c>
-      <c r="E5" s="64" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="65">
-        <f ca="1">TODAY()</f>
-        <v>46322</v>
-      </c>
-      <c r="G5" s="65">
-        <v>45956</v>
-      </c>
-      <c r="H5" s="64">
-        <f t="shared" ca="1" si="0"/>
-        <v>366</v>
-      </c>
-      <c r="I5" s="64" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" s="64">
-        <v>8</v>
-      </c>
-      <c r="K5" s="71">
+      <c r="J5" s="71">
         <v>4</v>
       </c>
-      <c r="L5" s="75">
+      <c r="K5" s="75">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="M5" s="71"/>
-    </row>
-    <row r="6" spans="1:13" s="67" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L5" s="71"/>
+    </row>
+    <row r="6" spans="1:12" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="67" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B6" s="67" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="67" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D6" s="67" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="68">
+        <f t="shared" ref="E6:E14" ca="1" si="2">TODAY()</f>
+        <v>46323</v>
+      </c>
+      <c r="F6" s="68">
+        <v>45910</v>
+      </c>
+      <c r="G6" s="67">
+        <f t="shared" ca="1" si="0"/>
+        <v>413</v>
+      </c>
+      <c r="H6" s="67" t="s">
+        <v>54</v>
+      </c>
+      <c r="I6" s="67">
+        <v>6</v>
+      </c>
+      <c r="J6" s="64">
         <v>1</v>
       </c>
-      <c r="E6" s="67" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="68">
-        <f t="shared" ref="F6:F14" ca="1" si="2">TODAY()</f>
-        <v>46322</v>
-      </c>
-      <c r="G6" s="68">
-        <v>45910</v>
-      </c>
-      <c r="H6" s="67">
-        <f t="shared" ca="1" si="0"/>
-        <v>412</v>
-      </c>
-      <c r="I6" s="67" t="s">
-        <v>54</v>
-      </c>
-      <c r="J6" s="67">
-        <v>6</v>
-      </c>
-      <c r="K6" s="64">
-        <v>1</v>
-      </c>
-      <c r="L6" s="66">
+      <c r="K6" s="66">
         <f t="shared" si="1"/>
         <v>0.16666666666666666</v>
       </c>
-      <c r="M6" s="64"/>
-    </row>
-    <row r="7" spans="1:13" s="64" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L6" s="64"/>
+    </row>
+    <row r="7" spans="1:12" s="64" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="64" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B7" s="64" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D7" s="64" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="64" t="s">
         <v>29</v>
       </c>
+      <c r="E7" s="65">
+        <f ca="1">TODAY()</f>
+        <v>46323</v>
+      </c>
       <c r="F7" s="65">
-        <f ca="1">TODAY()</f>
-        <v>46322</v>
-      </c>
-      <c r="G7" s="65">
         <v>46027</v>
       </c>
-      <c r="H7" s="64">
+      <c r="G7" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>295</v>
-      </c>
-      <c r="I7" s="64" t="s">
+        <v>296</v>
+      </c>
+      <c r="H7" s="64" t="s">
         <v>54</v>
       </c>
+      <c r="I7" s="64">
+        <v>7</v>
+      </c>
       <c r="J7" s="64">
-        <v>7</v>
-      </c>
-      <c r="K7" s="64">
         <v>1</v>
       </c>
-      <c r="L7" s="66">
+      <c r="K7" s="66">
         <f t="shared" si="1"/>
         <v>0.14285714285714285</v>
       </c>
     </row>
-    <row r="8" spans="1:13" s="71" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" s="71" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="71" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B8" s="71" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="71" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="71" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="72">
+        <f ca="1">TODAY()</f>
+        <v>46323</v>
+      </c>
+      <c r="F8" s="72">
+        <v>46036</v>
+      </c>
+      <c r="G8" s="71">
+        <f t="shared" ca="1" si="0"/>
+        <v>287</v>
+      </c>
+      <c r="H8" s="71" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" s="71">
         <v>9</v>
       </c>
-      <c r="D8" s="71" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="71" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="72">
-        <f ca="1">TODAY()</f>
-        <v>46322</v>
-      </c>
-      <c r="G8" s="72">
-        <v>46036</v>
-      </c>
-      <c r="H8" s="71">
-        <f t="shared" ca="1" si="0"/>
-        <v>286</v>
-      </c>
-      <c r="I8" s="71" t="s">
-        <v>54</v>
-      </c>
       <c r="J8" s="71">
-        <v>9</v>
-      </c>
-      <c r="K8" s="71">
         <v>3</v>
       </c>
-      <c r="L8" s="75">
+      <c r="K8" s="75">
         <f t="shared" si="1"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="71" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" s="71" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="71" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="B9" s="71" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C9" s="71" t="s">
         <v>76</v>
       </c>
       <c r="D9" s="71" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" s="71" t="s">
         <v>29</v>
       </c>
+      <c r="E9" s="72">
+        <f t="shared" ca="1" si="2"/>
+        <v>46323</v>
+      </c>
       <c r="F9" s="72">
-        <f t="shared" ca="1" si="2"/>
-        <v>46322</v>
-      </c>
-      <c r="G9" s="72">
         <v>46082</v>
       </c>
-      <c r="H9" s="71">
-        <f ca="1">F9-G9</f>
-        <v>240</v>
-      </c>
-      <c r="I9" s="71" t="s">
+      <c r="G9" s="71">
+        <f ca="1">E9-F9</f>
+        <v>241</v>
+      </c>
+      <c r="H9" s="71" t="s">
         <v>54</v>
       </c>
+      <c r="I9" s="71">
+        <v>10</v>
+      </c>
       <c r="J9" s="71">
-        <v>10</v>
-      </c>
-      <c r="K9" s="71">
         <v>4</v>
       </c>
-      <c r="L9" s="75">
+      <c r="K9" s="75">
         <f t="shared" si="1"/>
         <v>0.4</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="17" t="s">
         <v>29</v>
       </c>
+      <c r="E10" s="18">
+        <f t="shared" ca="1" si="2"/>
+        <v>46323</v>
+      </c>
       <c r="F10" s="18">
-        <f t="shared" ca="1" si="2"/>
-        <v>46322</v>
-      </c>
-      <c r="G10" s="18">
         <v>46089</v>
       </c>
-      <c r="H10" s="17">
-        <f t="shared" ref="H10:H17" ca="1" si="3">F10-G10</f>
-        <v>233</v>
-      </c>
-      <c r="I10" s="17" t="s">
+      <c r="G10" s="17">
+        <f t="shared" ref="G10:G17" ca="1" si="3">E10-F10</f>
+        <v>234</v>
+      </c>
+      <c r="H10" s="17" t="s">
         <v>54</v>
       </c>
+      <c r="I10" s="17">
+        <v>10</v>
+      </c>
       <c r="J10" s="17">
-        <v>10</v>
-      </c>
-      <c r="K10" s="17">
         <v>5</v>
       </c>
-      <c r="L10" s="22">
+      <c r="K10" s="22">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="69" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" s="69" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="69" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B11" s="69" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="69" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D11" s="69" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="69" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="18">
+      <c r="E11" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46322</v>
-      </c>
-      <c r="G11" s="70">
+        <v>46323</v>
+      </c>
+      <c r="F11" s="70">
         <v>46129</v>
       </c>
-      <c r="H11" s="17">
+      <c r="G11" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>193</v>
-      </c>
-      <c r="I11" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="H11" s="17" t="s">
         <v>54</v>
+      </c>
+      <c r="I11" s="69">
+        <v>8</v>
       </c>
       <c r="J11" s="69">
         <v>8</v>
       </c>
-      <c r="K11" s="69">
-        <v>8</v>
-      </c>
-      <c r="L11" s="22">
+      <c r="K11" s="22">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:13" s="69" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" s="69" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="69" t="s">
+        <v>79</v>
+      </c>
       <c r="C12" s="69" t="s">
         <v>80</v>
       </c>
       <c r="D12" s="69" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="18">
+      <c r="E12" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46322</v>
-      </c>
-      <c r="G12" s="70">
+        <v>46323</v>
+      </c>
+      <c r="F12" s="70">
         <v>46129</v>
       </c>
-      <c r="H12" s="17">
+      <c r="G12" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>193</v>
-      </c>
-      <c r="I12" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="H12" s="17" t="s">
         <v>54</v>
       </c>
+      <c r="I12" s="69">
+        <v>3</v>
+      </c>
       <c r="J12" s="69">
-        <v>3</v>
-      </c>
-      <c r="K12" s="69">
         <v>0</v>
       </c>
-      <c r="L12" s="22">
+      <c r="K12" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" s="71" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="71" t="s">
+        <v>83</v>
+      </c>
       <c r="C13" s="71" t="s">
         <v>84</v>
       </c>
       <c r="D13" s="71" t="s">
-        <v>85</v>
-      </c>
-      <c r="E13" s="71" t="s">
         <v>29</v>
       </c>
+      <c r="E13" s="72">
+        <f t="shared" ca="1" si="2"/>
+        <v>46323</v>
+      </c>
       <c r="F13" s="72">
-        <f t="shared" ca="1" si="2"/>
-        <v>46322</v>
-      </c>
-      <c r="G13" s="72">
         <v>46182</v>
       </c>
-      <c r="H13" s="71">
+      <c r="G13" s="71">
         <f t="shared" ca="1" si="3"/>
-        <v>140</v>
-      </c>
-      <c r="I13" s="71" t="s">
+        <v>141</v>
+      </c>
+      <c r="H13" s="71" t="s">
         <v>54</v>
       </c>
+      <c r="I13" s="71">
+        <v>4</v>
+      </c>
       <c r="J13" s="71">
-        <v>4</v>
-      </c>
-      <c r="K13" s="71">
         <v>3</v>
       </c>
-      <c r="L13" s="75">
+      <c r="K13" s="75">
         <f t="shared" si="1"/>
         <v>0.75</v>
       </c>
     </row>
-    <row r="14" spans="1:13" s="71" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="71" t="s">
+        <v>85</v>
+      </c>
       <c r="C14" s="71" t="s">
         <v>86</v>
       </c>
       <c r="D14" s="71" t="s">
-        <v>87</v>
-      </c>
-      <c r="E14" s="71" t="s">
         <v>34</v>
       </c>
+      <c r="E14" s="72">
+        <f t="shared" ca="1" si="2"/>
+        <v>46323</v>
+      </c>
       <c r="F14" s="72">
-        <f t="shared" ca="1" si="2"/>
-        <v>46322</v>
-      </c>
-      <c r="G14" s="72">
         <v>46184</v>
       </c>
-      <c r="H14" s="71">
+      <c r="G14" s="71">
         <f t="shared" ca="1" si="3"/>
-        <v>138</v>
-      </c>
-      <c r="I14" s="71" t="s">
+        <v>139</v>
+      </c>
+      <c r="H14" s="71" t="s">
         <v>54</v>
+      </c>
+      <c r="I14" s="71">
+        <v>1</v>
       </c>
       <c r="J14" s="71">
         <v>1</v>
       </c>
-      <c r="K14" s="71">
-        <v>1</v>
-      </c>
-      <c r="L14" s="75">
+      <c r="K14" s="75">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="17" t="s">
+        <v>90</v>
+      </c>
       <c r="C15" s="17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="E15" s="17" t="s">
         <v>34</v>
       </c>
+      <c r="E15" s="18">
+        <f ca="1">TODAY()</f>
+        <v>46323</v>
+      </c>
       <c r="F15" s="18">
-        <f ca="1">TODAY()</f>
-        <v>46322</v>
-      </c>
-      <c r="G15" s="18">
         <v>46216</v>
       </c>
-      <c r="H15" s="17">
+      <c r="G15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>106</v>
-      </c>
-      <c r="I15" s="69" t="s">
+        <v>107</v>
+      </c>
+      <c r="H15" s="69" t="s">
         <v>54</v>
+      </c>
+      <c r="I15" s="69">
+        <v>8</v>
       </c>
       <c r="J15" s="69">
         <v>8</v>
       </c>
-      <c r="K15" s="69">
-        <v>8</v>
-      </c>
-      <c r="L15" s="22">
-        <f>K15/J15</f>
+      <c r="K15" s="22">
+        <f>J15/I15</f>
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:13" s="71" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" s="71" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="71" t="s">
+        <v>91</v>
+      </c>
       <c r="C16" s="71" t="s">
         <v>92</v>
       </c>
       <c r="D16" s="71" t="s">
-        <v>93</v>
-      </c>
-      <c r="E16" s="71" t="s">
         <v>29</v>
       </c>
+      <c r="E16" s="72">
+        <f ca="1">TODAY()</f>
+        <v>46323</v>
+      </c>
       <c r="F16" s="72">
-        <f ca="1">TODAY()</f>
-        <v>46322</v>
-      </c>
-      <c r="G16" s="72">
-        <f t="shared" ref="G16" ca="1" si="4">TODAY()</f>
-        <v>46322</v>
-      </c>
-      <c r="H16" s="71">
+        <f t="shared" ref="F16" ca="1" si="4">TODAY()</f>
+        <v>46323</v>
+      </c>
+      <c r="G16" s="71">
         <f t="shared" ca="1" si="3"/>
         <v>0</v>
       </c>
-      <c r="I16" s="71" t="s">
+      <c r="H16" s="71" t="s">
         <v>54</v>
+      </c>
+      <c r="I16" s="71">
+        <v>6</v>
       </c>
       <c r="J16" s="71">
         <v>6</v>
       </c>
-      <c r="K16" s="71">
+      <c r="K16" s="75">
+        <f>J16/I16</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="18">
+        <f ca="1">TODAY()</f>
+        <v>46323</v>
+      </c>
+      <c r="F17" s="18">
+        <v>46271</v>
+      </c>
+      <c r="G17" s="17">
+        <f t="shared" ca="1" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="H17" s="69" t="s">
+        <v>54</v>
+      </c>
+      <c r="I17" s="69">
         <v>6</v>
-      </c>
-      <c r="L16" s="75">
-        <f>K16/J16</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" s="18">
-        <f ca="1">TODAY()</f>
-        <v>46322</v>
-      </c>
-      <c r="G17" s="18">
-        <v>46271</v>
-      </c>
-      <c r="H17" s="17">
-        <f t="shared" ca="1" si="3"/>
-        <v>51</v>
-      </c>
-      <c r="I17" s="69" t="s">
-        <v>54</v>
       </c>
       <c r="J17" s="69">
         <v>6</v>
       </c>
-      <c r="K17" s="69">
-        <v>6</v>
-      </c>
-      <c r="L17" s="22">
-        <f>K17/J17</f>
+      <c r="K17" s="22">
+        <f>J17/I17</f>
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E18" s="18"/>
       <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
+      <c r="H18" s="69"/>
       <c r="I18" s="69"/>
       <c r="J18" s="69"/>
-      <c r="K18" s="69"/>
-      <c r="L18" s="22" t="e">
-        <f t="shared" ref="L18:L23" si="5">K18/J18</f>
+      <c r="K18" s="22" t="e">
+        <f t="shared" ref="K18:K23" si="5">J18/I18</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="19" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="73"/>
       <c r="C19" s="73"/>
       <c r="D19" s="73"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="17"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="69"/>
       <c r="I19" s="69"/>
       <c r="J19" s="69"/>
-      <c r="K19" s="69"/>
-      <c r="L19" s="22" t="e">
+      <c r="K19" s="22" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M19" s="17"/>
-    </row>
-    <row r="20" spans="1:13" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L19" s="17"/>
+    </row>
+    <row r="20" spans="1:12" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="C20" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="31" t="s">
+      <c r="D20" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="31">
+      <c r="E20" s="31">
         <v>45997</v>
       </c>
-      <c r="I20" s="32"/>
-      <c r="L20" s="91" t="e">
+      <c r="H20" s="32"/>
+      <c r="K20" s="91" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="21" spans="1:13" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" s="92" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="92" t="s">
+        <v>9</v>
+      </c>
       <c r="B21" s="92" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="92" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D21" s="92" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="92" t="s">
         <v>29</v>
       </c>
+      <c r="E21" s="93">
+        <f ca="1">TODAY()</f>
+        <v>46323</v>
+      </c>
       <c r="F21" s="93">
-        <f ca="1">TODAY()</f>
-        <v>46322</v>
-      </c>
-      <c r="G21" s="93">
         <v>46311</v>
       </c>
-      <c r="H21" s="92">
+      <c r="G21" s="92">
         <v>12</v>
       </c>
-      <c r="I21" s="92" t="s">
+      <c r="H21" s="92" t="s">
         <v>54</v>
+      </c>
+      <c r="I21" s="92">
+        <v>1</v>
       </c>
       <c r="J21" s="92">
         <v>1</v>
       </c>
-      <c r="K21" s="92">
+      <c r="K21" s="94">
+        <f>J21/I21</f>
         <v>1</v>
       </c>
-      <c r="L21" s="94">
-        <f>K21/J21</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:12" s="92" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="92" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="B22" s="92" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C22" s="92" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D22" s="92" t="s">
-        <v>90</v>
-      </c>
-      <c r="E22" s="92" t="s">
         <v>34</v>
       </c>
+      <c r="E22" s="93">
+        <f t="shared" ref="E22:E23" ca="1" si="6">TODAY()</f>
+        <v>46323</v>
+      </c>
       <c r="F22" s="93">
-        <f t="shared" ref="F22:F23" ca="1" si="6">TODAY()</f>
         <v>46322</v>
       </c>
-      <c r="G22" s="93">
-        <v>46322</v>
-      </c>
-      <c r="H22" s="92">
+      <c r="G22" s="92">
         <v>12</v>
       </c>
-      <c r="I22" s="92" t="s">
+      <c r="H22" s="92" t="s">
         <v>54</v>
+      </c>
+      <c r="I22" s="92">
+        <v>8</v>
       </c>
       <c r="J22" s="92">
         <v>8</v>
       </c>
-      <c r="K22" s="92">
-        <v>8</v>
-      </c>
-      <c r="L22" s="94">
+      <c r="K22" s="94">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:13" s="92" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" s="92" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="92" t="s">
+        <v>95</v>
+      </c>
       <c r="B23" s="92" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C23" s="92" t="s">
         <v>96</v>
       </c>
       <c r="D23" s="92" t="s">
-        <v>97</v>
-      </c>
-      <c r="E23" s="92" t="s">
         <v>29</v>
       </c>
+      <c r="E23" s="93">
+        <f t="shared" ca="1" si="6"/>
+        <v>46323</v>
+      </c>
       <c r="F23" s="93">
-        <f t="shared" ca="1" si="6"/>
         <v>46322</v>
       </c>
-      <c r="G23" s="93">
-        <v>46322</v>
-      </c>
-      <c r="H23" s="92">
+      <c r="G23" s="92">
         <v>12</v>
       </c>
-      <c r="I23" s="92" t="s">
+      <c r="H23" s="92" t="s">
         <v>54</v>
+      </c>
+      <c r="I23" s="92">
+        <v>1</v>
       </c>
       <c r="J23" s="92">
         <v>1</v>
       </c>
-      <c r="K23" s="92">
-        <v>1</v>
-      </c>
-      <c r="L23" s="94">
+      <c r="K23" s="94">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:13" s="95" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" s="95" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="E24" s="96"/>
       <c r="F24" s="96"/>
-      <c r="G24" s="96"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -3597,813 +3558,814 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C21D6C99-536E-4F31-8A16-5ECA51AF8689}">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" style="21" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="21"/>
-    <col min="3" max="3" width="19.42578125" style="21" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="21" customWidth="1"/>
-    <col min="5" max="5" width="13" style="81" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" style="81" customWidth="1"/>
-    <col min="7" max="7" width="13" style="21" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" style="21" customWidth="1"/>
-    <col min="9" max="9" width="15.28515625" style="90" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" style="21" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="21"/>
+    <col min="1" max="1" width="9.140625" style="21"/>
+    <col min="2" max="2" width="19.42578125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" style="21" customWidth="1"/>
+    <col min="4" max="4" width="13" style="81" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" style="81" customWidth="1"/>
+    <col min="6" max="6" width="13" style="21" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="21" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" style="90" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" style="21" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="49" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B1" s="46" t="s">
+    <row r="1" spans="1:9" s="49" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="46">
+      <c r="B1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
-      </c>
+        <v>46323</v>
+      </c>
+      <c r="D1" s="46"/>
       <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="52" t="e">
-        <f>AVERAGE(I:I)</f>
+      <c r="F1" s="52" t="e">
+        <f>AVERAGE(H:H)</f>
         <v>#REF!</v>
       </c>
-      <c r="H1" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="I1" s="52"/>
-    </row>
-    <row r="2" spans="1:10" s="55" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
+      <c r="G1" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="52"/>
+    </row>
+    <row r="2" spans="1:9" s="55" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="56" t="s">
         <v>59</v>
       </c>
       <c r="B2" s="56" t="s">
-        <v>60</v>
-      </c>
-      <c r="C2" s="56" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" s="55" t="s">
         <v>65</v>
       </c>
+      <c r="C2" s="55" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="56" t="s">
+        <v>67</v>
+      </c>
       <c r="E2" s="56" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="55" t="s">
         <v>68</v>
-      </c>
-      <c r="F2" s="56" t="s">
-        <v>62</v>
       </c>
       <c r="G2" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="55" t="s">
+      <c r="H2" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="87" t="s">
-        <v>71</v>
-      </c>
-      <c r="J2" s="55" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I2" s="55" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="58" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B3" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="59">
+        <v>45955</v>
+      </c>
+      <c r="E3" s="59">
+        <v>45977</v>
+      </c>
+      <c r="F3" s="58">
+        <f>E3-D3</f>
+        <v>22</v>
+      </c>
+      <c r="G3" s="58">
+        <v>10</v>
+      </c>
+      <c r="H3" s="60">
+        <f>I3/G3</f>
+        <v>1</v>
+      </c>
+      <c r="I3" s="58">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="58" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="58" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="58" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="59">
+        <v>45982</v>
+      </c>
+      <c r="E4" s="59">
+        <v>46003</v>
+      </c>
+      <c r="F4" s="58">
+        <f>E4-D4</f>
+        <v>21</v>
+      </c>
+      <c r="G4" s="58">
+        <v>10</v>
+      </c>
+      <c r="H4" s="60">
+        <f>I4/G4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="61" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="61" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="61" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="62">
+        <v>46005</v>
+      </c>
+      <c r="E5" s="62">
+        <v>46026</v>
+      </c>
+      <c r="F5" s="61">
+        <f>E5-D5</f>
+        <v>21</v>
+      </c>
+      <c r="G5" s="61">
+        <v>10</v>
+      </c>
+      <c r="H5" s="63" t="e">
+        <f>#REF!/G5</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="B6" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="58" t="s">
+      <c r="C6" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="59">
-        <v>45955</v>
-      </c>
-      <c r="F3" s="59">
-        <v>45977</v>
-      </c>
-      <c r="G3" s="58">
-        <f>F3-E3</f>
-        <v>22</v>
-      </c>
-      <c r="H3" s="58">
+      <c r="D6" s="62">
+        <v>46015</v>
+      </c>
+      <c r="E6" s="62">
+        <v>46036</v>
+      </c>
+      <c r="F6" s="61">
+        <f>E6-D6</f>
+        <v>21</v>
+      </c>
+      <c r="G6" s="61">
         <v>10</v>
       </c>
-      <c r="I3" s="60">
-        <f>J3/H3</f>
-        <v>1</v>
-      </c>
-      <c r="J3" s="58">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" s="58" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="58" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="58" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="58" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4" s="59">
-        <v>45982</v>
-      </c>
-      <c r="F4" s="59">
-        <v>46003</v>
-      </c>
-      <c r="G4" s="58">
-        <f>F4-E4</f>
-        <v>21</v>
-      </c>
-      <c r="H4" s="58">
-        <v>10</v>
-      </c>
-      <c r="I4" s="60">
-        <f>J4/H4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="58" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="61" t="s">
+      <c r="H6" s="63">
+        <f>I6/G6</f>
+        <v>0.9</v>
+      </c>
+      <c r="I6" s="61">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="H7" s="63"/>
+    </row>
+    <row r="9" spans="1:9" s="64" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="61" t="s">
+      <c r="B9" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="61" t="s">
+      <c r="C9" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="62">
-        <v>46005</v>
-      </c>
-      <c r="F5" s="62">
-        <v>46026</v>
-      </c>
-      <c r="G5" s="61">
-        <f>F5-E5</f>
-        <v>21</v>
-      </c>
-      <c r="H5" s="61">
-        <v>10</v>
-      </c>
-      <c r="I5" s="63" t="e">
-        <f>#REF!/H5</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="61" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="61" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="61" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="62">
-        <v>46015</v>
-      </c>
-      <c r="F6" s="62">
-        <v>46036</v>
-      </c>
-      <c r="G6" s="61">
-        <f>F6-E6</f>
-        <v>21</v>
-      </c>
-      <c r="H6" s="61">
-        <v>10</v>
-      </c>
-      <c r="I6" s="63">
-        <f>J6/H6</f>
-        <v>0.9</v>
-      </c>
-      <c r="J6" s="61">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
-      <c r="I7" s="63"/>
-    </row>
-    <row r="9" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="64" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="64" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="64" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="64" t="s">
-        <v>29</v>
+      <c r="D9" s="65">
+        <v>46106</v>
       </c>
       <c r="E9" s="65">
-        <v>46106</v>
-      </c>
-      <c r="F9" s="65">
         <v>46129</v>
       </c>
+      <c r="F9" s="64">
+        <f>E9-D9</f>
+        <v>23</v>
+      </c>
       <c r="G9" s="64">
-        <f>F9-E9</f>
-        <v>23</v>
-      </c>
-      <c r="H9" s="64">
         <v>13</v>
       </c>
-      <c r="I9" s="66">
-        <f>J9/H9</f>
+      <c r="H9" s="66">
+        <f>I9/G9</f>
         <v>0.61538461538461542</v>
       </c>
-      <c r="J9" s="64">
+      <c r="I9" s="64">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" s="64" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="64" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="B10" s="64" t="s">
         <v>80</v>
       </c>
       <c r="C10" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="65">
+        <v>46106</v>
+      </c>
+      <c r="E10" s="65">
+        <v>46129</v>
+      </c>
+      <c r="F10" s="64">
+        <f>E10-D10</f>
+        <v>23</v>
+      </c>
+      <c r="G10" s="64">
+        <v>13</v>
+      </c>
+      <c r="H10" s="66">
+        <f>I10/G10</f>
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="I10" s="64">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="64" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="64" t="s">
         <v>81</v>
-      </c>
-      <c r="D10" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="65">
-        <v>46106</v>
-      </c>
-      <c r="F10" s="65">
-        <v>46129</v>
-      </c>
-      <c r="G10" s="64">
-        <f>F10-E10</f>
-        <v>23</v>
-      </c>
-      <c r="H10" s="64">
-        <v>13</v>
-      </c>
-      <c r="I10" s="66">
-        <f>J10/H10</f>
-        <v>0.23076923076923078</v>
-      </c>
-      <c r="J10" s="64">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" s="64" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="64" t="s">
-        <v>17</v>
       </c>
       <c r="B11" s="64" t="s">
         <v>82</v>
       </c>
       <c r="C11" s="64" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="65">
+        <v>46122</v>
+      </c>
+      <c r="E11" s="65">
+        <v>46144</v>
+      </c>
+      <c r="F11" s="64">
+        <f>E11-D11</f>
+        <v>22</v>
+      </c>
+      <c r="G11" s="64">
+        <v>13</v>
+      </c>
+      <c r="H11" s="66">
+        <f>I11/G11</f>
+        <v>0.38461538461538464</v>
+      </c>
+      <c r="I11" s="64">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="16">
+        <v>46124</v>
+      </c>
+      <c r="E12" s="16">
+        <v>46145</v>
+      </c>
+      <c r="F12" s="15">
+        <f>E12-D12</f>
+        <v>21</v>
+      </c>
+      <c r="G12" s="15">
+        <v>13</v>
+      </c>
+      <c r="H12" s="33">
+        <f>I12/G12</f>
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="I12" s="15">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="H13" s="33"/>
+    </row>
+    <row r="14" spans="1:9" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="77" t="s">
         <v>83</v>
       </c>
-      <c r="D11" s="64" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="65">
-        <v>46122</v>
-      </c>
-      <c r="F11" s="65">
-        <v>46144</v>
-      </c>
-      <c r="G11" s="64">
-        <f>F11-E11</f>
-        <v>22</v>
-      </c>
-      <c r="H11" s="64">
-        <v>13</v>
-      </c>
-      <c r="I11" s="66">
-        <f>J11/H11</f>
-        <v>0.38461538461538464</v>
-      </c>
-      <c r="J11" s="64">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="16">
-        <v>46124</v>
-      </c>
-      <c r="F12" s="16">
-        <v>46145</v>
-      </c>
-      <c r="G12" s="15">
-        <f>F12-E12</f>
-        <v>21</v>
-      </c>
-      <c r="H12" s="15">
-        <v>13</v>
-      </c>
-      <c r="I12" s="33">
-        <f>J12/H12</f>
-        <v>0.84615384615384615</v>
-      </c>
-      <c r="J12" s="15">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="I13" s="33"/>
-    </row>
-    <row r="14" spans="1:10" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="77" t="s">
         <v>84</v>
       </c>
       <c r="C14" s="77" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="79">
+        <v>46159</v>
+      </c>
+      <c r="E14" s="79">
+        <v>46182</v>
+      </c>
+      <c r="F14" s="77">
+        <f>E14-D14</f>
+        <v>23</v>
+      </c>
+      <c r="G14" s="77">
+        <v>12</v>
+      </c>
+      <c r="H14" s="88">
+        <f>I14/G14</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="I14" s="77">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="D14" s="77" t="s">
-        <v>29</v>
-      </c>
-      <c r="E14" s="79">
-        <v>46159</v>
-      </c>
-      <c r="F14" s="79">
-        <v>46182</v>
-      </c>
-      <c r="G14" s="77">
-        <f>F14-E14</f>
-        <v>23</v>
-      </c>
-      <c r="H14" s="77">
-        <v>12</v>
-      </c>
-      <c r="I14" s="88">
-        <f>J14/H14</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J14" s="77">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="77" t="s">
         <v>86</v>
       </c>
       <c r="C15" s="77" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="79">
+        <v>46169</v>
+      </c>
+      <c r="E15" s="79">
+        <v>46190</v>
+      </c>
+      <c r="F15" s="77">
+        <f>E15-D15</f>
+        <v>21</v>
+      </c>
+      <c r="G15" s="77">
+        <v>12</v>
+      </c>
+      <c r="H15" s="88" t="s">
         <v>87</v>
       </c>
-      <c r="D15" s="77" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="79">
-        <v>46169</v>
-      </c>
-      <c r="F15" s="79">
-        <v>46190</v>
-      </c>
-      <c r="G15" s="77">
-        <f>F15-E15</f>
-        <v>21</v>
-      </c>
-      <c r="H15" s="77">
-        <v>12</v>
-      </c>
-      <c r="I15" s="88" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" s="77" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:9" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="77" t="s">
+        <v>85</v>
+      </c>
       <c r="B16" s="77" t="s">
         <v>86</v>
       </c>
       <c r="C16" s="77" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" s="77" t="s">
         <v>34</v>
       </c>
+      <c r="D16" s="79">
+        <v>46171</v>
+      </c>
       <c r="E16" s="79">
-        <v>46171</v>
-      </c>
-      <c r="F16" s="79">
         <v>46184</v>
       </c>
+      <c r="F16" s="77">
+        <f>E16-D16</f>
+        <v>13</v>
+      </c>
       <c r="G16" s="77">
-        <f>F16-E16</f>
-        <v>13</v>
-      </c>
-      <c r="H16" s="77">
         <v>3</v>
       </c>
-      <c r="I16" s="88">
-        <f>J16/H16</f>
+      <c r="H16" s="88">
+        <f>I16/G16</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="J16" s="77">
+      <c r="I16" s="77">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" s="17" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="77" t="s">
+        <v>8</v>
+      </c>
       <c r="C17" s="77" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="79">
+        <v>46188</v>
+      </c>
+      <c r="E17" s="79">
+        <v>46209</v>
+      </c>
+      <c r="F17" s="77">
+        <f>E17-D17</f>
+        <v>21</v>
+      </c>
+      <c r="G17" s="77">
+        <v>12</v>
+      </c>
+      <c r="H17" s="88">
+        <f>I17/G17</f>
+        <v>1</v>
+      </c>
+      <c r="I17" s="77">
+        <v>12</v>
+      </c>
+      <c r="J17" s="77"/>
+    </row>
+    <row r="18" spans="1:10" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="77" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="77" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="77" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="79">
+        <v>46194</v>
+      </c>
+      <c r="E18" s="79">
+        <v>46215</v>
+      </c>
+      <c r="F18" s="77">
+        <f>E18-D18</f>
+        <v>21</v>
+      </c>
+      <c r="G18" s="77">
+        <v>12</v>
+      </c>
+      <c r="H18" s="88">
+        <f>I18/G18</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="I18" s="77">
         <v>8</v>
       </c>
-      <c r="D17" s="77" t="s">
+    </row>
+    <row r="19" spans="1:10" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="77" t="s">
+        <v>7</v>
+      </c>
+      <c r="H19" s="88"/>
+    </row>
+    <row r="20" spans="1:10" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="77" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="77" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="79">
-        <v>46188</v>
-      </c>
-      <c r="F17" s="79">
-        <v>46209</v>
-      </c>
-      <c r="G17" s="77">
-        <f>F17-E17</f>
-        <v>21</v>
-      </c>
-      <c r="H17" s="77">
+      <c r="D20" s="79">
+        <v>46221</v>
+      </c>
+      <c r="E20" s="79">
+        <v>46245</v>
+      </c>
+      <c r="F20" s="77">
+        <f t="shared" ref="F20:F25" si="0">E20-D20</f>
+        <v>24</v>
+      </c>
+      <c r="G20" s="77">
         <v>12</v>
       </c>
-      <c r="I17" s="88">
-        <f>J17/H17</f>
-        <v>1</v>
-      </c>
-      <c r="J17" s="77">
-        <v>12</v>
-      </c>
-      <c r="K17" s="77"/>
-    </row>
-    <row r="18" spans="1:11" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="77" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="77" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" s="77" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" s="77" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" s="79">
-        <v>46194</v>
-      </c>
-      <c r="F18" s="79">
-        <v>46215</v>
-      </c>
-      <c r="G18" s="77">
-        <f>F18-E18</f>
-        <v>21</v>
-      </c>
-      <c r="H18" s="77">
-        <v>12</v>
-      </c>
-      <c r="I18" s="88">
-        <f>J18/H18</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J18" s="77">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="77" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="77" t="s">
-        <v>7</v>
-      </c>
-      <c r="I19" s="88"/>
-    </row>
-    <row r="20" spans="1:11" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="77" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="77" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="77" t="s">
+      <c r="H20" s="88">
+        <f t="shared" ref="H20:H25" si="1">I20/G20</f>
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="I20" s="77">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="77" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="77" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="79">
-        <v>46221</v>
-      </c>
-      <c r="F20" s="79">
+      <c r="D21" s="79">
+        <v>46223</v>
+      </c>
+      <c r="E21" s="79">
         <v>46245</v>
       </c>
-      <c r="G20" s="77">
-        <f t="shared" ref="G20:G25" si="0">F20-E20</f>
-        <v>24</v>
-      </c>
-      <c r="H20" s="77">
-        <v>12</v>
-      </c>
-      <c r="I20" s="88">
-        <f t="shared" ref="I20:I25" si="1">J20/H20</f>
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="J20" s="77">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" s="77" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="77" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="77" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="79">
-        <v>46223</v>
-      </c>
-      <c r="F21" s="79">
-        <v>46245</v>
-      </c>
-      <c r="G21" s="77">
+      <c r="F21" s="77">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="H21" s="77">
+      <c r="G21" s="77">
         <v>12</v>
       </c>
-      <c r="I21" s="88">
+      <c r="H21" s="88">
         <f t="shared" si="1"/>
         <v>0.58333333333333337</v>
       </c>
-      <c r="J21" s="77">
+      <c r="I21" s="77">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="77" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="77" t="s">
+        <v>79</v>
+      </c>
       <c r="B22" s="77" t="s">
         <v>80</v>
       </c>
       <c r="C22" s="77" t="s">
-        <v>81</v>
-      </c>
-      <c r="D22" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="79" t="s">
-        <v>94</v>
-      </c>
-      <c r="F22" s="79">
+      <c r="D22" s="79" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" s="79">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
-      </c>
-      <c r="G22" s="77" t="e">
+        <v>46323</v>
+      </c>
+      <c r="F22" s="77" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#VALUE!</v>
       </c>
-      <c r="I22" s="88" t="e">
+      <c r="H22" s="88" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="23" spans="1:11" s="77" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="77" t="s">
+        <v>91</v>
+      </c>
       <c r="B23" s="77" t="s">
         <v>92</v>
       </c>
       <c r="C23" s="77" t="s">
-        <v>93</v>
-      </c>
-      <c r="D23" s="77" t="s">
         <v>29</v>
       </c>
+      <c r="D23" s="79">
+        <v>46237</v>
+      </c>
       <c r="E23" s="79">
-        <v>46237</v>
-      </c>
-      <c r="F23" s="79">
         <v>46260</v>
       </c>
-      <c r="G23" s="77">
+      <c r="F23" s="77">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="H23" s="77">
+      <c r="G23" s="77">
         <v>10</v>
       </c>
-      <c r="I23" s="88">
+      <c r="H23" s="88">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
-      <c r="J23" s="77">
+      <c r="I23" s="77">
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:11" s="77" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" s="77" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="77" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="B24" s="77" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C24" s="77" t="s">
-        <v>90</v>
-      </c>
-      <c r="D24" s="77" t="s">
         <v>34</v>
       </c>
+      <c r="D24" s="79">
+        <v>46297</v>
+      </c>
       <c r="E24" s="79">
-        <v>46297</v>
-      </c>
-      <c r="F24" s="79">
         <v>46318</v>
       </c>
-      <c r="G24" s="77">
+      <c r="F24" s="77">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="H24" s="77">
+      <c r="G24" s="77">
         <v>12</v>
       </c>
-      <c r="I24" s="88">
+      <c r="H24" s="88">
         <f t="shared" si="1"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="J24" s="77">
+      <c r="I24" s="77">
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:11" s="77" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" s="77" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="77" t="s">
+        <v>95</v>
+      </c>
       <c r="B25" s="77" t="s">
         <v>96</v>
       </c>
       <c r="C25" s="77" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" s="77" t="s">
         <v>29</v>
       </c>
+      <c r="D25" s="79">
+        <v>46291</v>
+      </c>
       <c r="E25" s="79">
-        <v>46291</v>
-      </c>
-      <c r="F25" s="79">
         <v>46312</v>
       </c>
-      <c r="G25" s="77">
+      <c r="F25" s="77">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="H25" s="77">
+      <c r="G25" s="77">
         <v>12</v>
       </c>
-      <c r="I25" s="88">
+      <c r="H25" s="88">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:11" s="78" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="78" t="s">
+        <v>75</v>
+      </c>
       <c r="B27" s="78" t="s">
         <v>76</v>
       </c>
       <c r="C27" s="78" t="s">
-        <v>77</v>
-      </c>
-      <c r="D27" s="78" t="s">
         <v>29</v>
       </c>
+      <c r="D27" s="80">
+        <v>46316</v>
+      </c>
       <c r="E27" s="80">
-        <v>46316</v>
-      </c>
-      <c r="F27" s="80">
         <v>46337</v>
       </c>
+      <c r="F27" s="78">
+        <f>E27-D27</f>
+        <v>21</v>
+      </c>
       <c r="G27" s="78">
-        <f>F27-E27</f>
+        <v>12</v>
+      </c>
+      <c r="H27" s="89">
+        <f>I27/G27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="78" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="80">
+        <v>46323</v>
+      </c>
+      <c r="E28" s="80">
+        <v>46344</v>
+      </c>
+      <c r="F28" s="78">
+        <f>E28-D28</f>
         <v>21</v>
       </c>
-      <c r="H27" s="78">
+      <c r="G28" s="78">
         <v>12</v>
       </c>
-      <c r="I27" s="89">
-        <f>J27/H27</f>
+      <c r="H28" s="89">
+        <f>I28/G28</f>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:11" s="78" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="78" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="78" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" s="78" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29" s="80"/>
       <c r="E29" s="80"/>
-      <c r="F29" s="80"/>
-      <c r="I29" s="89"/>
-    </row>
-    <row r="30" spans="1:11" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H29" s="89" t="e">
+        <f t="shared" ref="H29" si="2">I29/G29</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D30" s="80"/>
       <c r="E30" s="80"/>
-      <c r="F30" s="80"/>
-      <c r="I30" s="89"/>
-    </row>
-    <row r="31" spans="1:11" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H30" s="89"/>
+    </row>
+    <row r="31" spans="1:10" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D31" s="80"/>
       <c r="E31" s="80"/>
-      <c r="F31" s="80"/>
-      <c r="I31" s="89"/>
-    </row>
-    <row r="32" spans="1:11" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="30" t="s">
+      <c r="H31" s="89"/>
+    </row>
+    <row r="32" spans="1:10" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D32" s="80"/>
+      <c r="E32" s="80"/>
+      <c r="H32" s="89"/>
+    </row>
+    <row r="33" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D33" s="31">
+        <v>45996</v>
+      </c>
+      <c r="E33" s="31"/>
+      <c r="H33" s="32"/>
+    </row>
+    <row r="35" spans="1:9" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="B32" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="D32" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="E32" s="31">
-        <v>45996</v>
-      </c>
-      <c r="F32" s="31"/>
-      <c r="I32" s="32"/>
-    </row>
-    <row r="34" spans="1:10" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="58"/>
-      <c r="B34" s="61" t="s">
+      <c r="B35" s="61" t="s">
         <v>76</v>
       </c>
-      <c r="C34" s="61" t="s">
-        <v>77</v>
-      </c>
-      <c r="D34" s="61" t="s">
+      <c r="C35" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="E34" s="62">
+      <c r="D35" s="62">
         <v>46060</v>
       </c>
-      <c r="F34" s="62">
+      <c r="E35" s="62">
         <v>46081</v>
       </c>
-      <c r="G34" s="61">
-        <f>F34-E34</f>
+      <c r="F35" s="61">
+        <f>E35-D35</f>
         <v>21</v>
       </c>
-      <c r="H34" s="61">
+      <c r="G35" s="61">
         <v>12</v>
       </c>
-      <c r="I34" s="63">
-        <f>J34/H34</f>
+      <c r="H35" s="63">
+        <f>I35/G35</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="J34" s="61">
+      <c r="I35" s="61">
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:10" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="61" t="s">
+    <row r="36" spans="1:9" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="61" t="s">
+      <c r="B36" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="D35" s="61" t="s">
+      <c r="C36" s="61" t="s">
         <v>29</v>
       </c>
-      <c r="E35" s="62">
+      <c r="D36" s="62">
         <v>46067</v>
       </c>
-      <c r="F35" s="62">
+      <c r="E36" s="62">
         <v>46088</v>
       </c>
-      <c r="G35" s="61">
-        <f>F35-E35</f>
+      <c r="F36" s="61">
+        <f>E36-D36</f>
         <v>21</v>
       </c>
-      <c r="H35" s="61">
+      <c r="G36" s="61">
         <v>12</v>
       </c>
-      <c r="I35" s="63">
-        <f>J35/H35</f>
+      <c r="H36" s="63">
+        <f>I36/G36</f>
         <v>0.41666666666666669</v>
       </c>
-      <c r="J35" s="61">
+      <c r="I36" s="61">
         <v>5</v>
       </c>
     </row>
@@ -4437,7 +4399,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="82" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C4" s="83">
         <v>50</v>
@@ -4447,7 +4409,7 @@
         <v>50</v>
       </c>
       <c r="G4" s="84" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H4" s="82">
         <f>SUM(A:A)</f>
@@ -4459,7 +4421,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="82" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C5" s="83">
         <v>50</v>
@@ -4469,7 +4431,7 @@
         <v>50</v>
       </c>
       <c r="G5" s="84" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H5" s="83">
         <f>SUM(D:D)</f>
@@ -4481,7 +4443,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="82" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" s="83">
         <v>35</v>
@@ -4491,7 +4453,7 @@
         <v>70</v>
       </c>
       <c r="G6" s="85" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H6" s="83">
         <f>H5/4</f>
@@ -4503,7 +4465,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="82" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="83">
         <v>30</v>
@@ -4513,7 +4475,7 @@
         <v>150</v>
       </c>
       <c r="G7" s="85" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H7" s="83">
         <f>H5-H6</f>
@@ -4525,7 +4487,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="82" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C8" s="83">
         <v>25</v>
@@ -4535,7 +4497,7 @@
         <v>50</v>
       </c>
       <c r="G8" s="85" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H8" s="83">
         <v>250</v>
@@ -4546,7 +4508,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="82" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C9" s="83">
         <v>30</v>

--- a/Galinhas/Galinhas 2026.xlsx
+++ b/Galinhas/Galinhas 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BichosDeCasa\Galinhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A322C0-4BCF-4D1A-9BC4-CF383366B752}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C36D875-16E9-4D8F-A352-4509D063FECA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="14370" windowHeight="3840" activeTab="2" xr2:uid="{0FF26368-0124-41AC-ABBE-7DCA2B31386A}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="106">
   <si>
     <t>HOJE</t>
   </si>
@@ -575,7 +575,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -864,6 +864,15 @@
     </xf>
     <xf numFmtId="14" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1201,7 +1210,7 @@
       </c>
       <c r="C1" s="40">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="D1" s="41">
         <f>SUM(I32:I43)</f>
@@ -1478,11 +1487,11 @@
       </c>
       <c r="E11" s="16">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" ref="F11:F18" ca="1" si="3">E11-D11</f>
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" ca="1" si="1"/>
@@ -1585,18 +1594,18 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="G15" s="17">
         <v>14</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" ca="1" si="1"/>
-        <v>2.7131782945736434E-2</v>
+        <v>2.7027027027027029E-2</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="17" customFormat="1" x14ac:dyDescent="0.25">
@@ -1696,18 +1705,18 @@
       </c>
       <c r="E19" s="16">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" ref="F19:F20" ca="1" si="4">E19-D19</f>
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="G19" s="15">
         <v>15</v>
       </c>
       <c r="H19" s="14">
         <f ca="1">G19/F19</f>
-        <v>3.3707865168539325E-2</v>
+        <v>3.3557046979865772E-2</v>
       </c>
       <c r="J19" s="15" t="s">
         <v>30</v>
@@ -1770,7 +1779,7 @@
       </c>
       <c r="I21" s="17">
         <f ca="1">E21-TODAY()</f>
-        <v>-413</v>
+        <v>-415</v>
       </c>
       <c r="J21" s="23" t="s">
         <v>23</v>
@@ -1805,7 +1814,7 @@
       </c>
       <c r="I22" s="17">
         <f ca="1">E22-TODAY()</f>
-        <v>-413</v>
+        <v>-415</v>
       </c>
       <c r="J22" s="23" t="s">
         <v>23</v>
@@ -1860,18 +1869,18 @@
       </c>
       <c r="E24" s="20">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F24" s="19">
         <f ca="1">E24-D24</f>
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="G24" s="19">
         <v>3</v>
       </c>
       <c r="H24" s="14">
         <f ca="1">G24/F24</f>
-        <v>7.1599045346062056E-3</v>
+        <v>7.1258907363420431E-3</v>
       </c>
       <c r="J24" s="19" t="s">
         <v>29</v>
@@ -1892,7 +1901,7 @@
       </c>
       <c r="E25" s="20">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F25" s="19">
         <v>6</v>
@@ -1923,18 +1932,18 @@
       </c>
       <c r="E26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F26" s="19">
         <f ca="1">E26-D26</f>
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="G26" s="19">
         <v>3</v>
       </c>
       <c r="H26" s="14">
         <f t="shared" ca="1" si="7"/>
-        <v>7.1599045346062056E-3</v>
+        <v>7.1258907363420431E-3</v>
       </c>
       <c r="J26" s="19" t="s">
         <v>29</v>
@@ -1955,18 +1964,18 @@
       </c>
       <c r="E27" s="20">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F27" s="19">
         <f ca="1">E27-D27</f>
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="G27" s="19">
         <v>3</v>
       </c>
       <c r="H27" s="14">
         <f t="shared" ref="H27" ca="1" si="8">G27/F27</f>
-        <v>7.1599045346062056E-3</v>
+        <v>7.1258907363420431E-3</v>
       </c>
       <c r="J27" s="19" t="s">
         <v>34</v>
@@ -2307,14 +2316,14 @@
       </c>
       <c r="D41" s="37">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="E41" s="37">
         <v>45910</v>
       </c>
       <c r="F41" s="28">
         <f ca="1">D41-E41</f>
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="G41" s="38" t="s">
         <v>54</v>
@@ -2339,14 +2348,14 @@
       </c>
       <c r="D42" s="18">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="E42" s="18">
         <v>45947</v>
       </c>
       <c r="F42" s="17">
         <f ca="1">D42-E42</f>
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>54</v>
@@ -2371,14 +2380,14 @@
       </c>
       <c r="D43" s="18">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="E43" s="18">
         <v>45953</v>
       </c>
       <c r="F43" s="17">
         <f t="shared" ref="F43:F44" ca="1" si="9">D43-E43</f>
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>54</v>
@@ -2403,14 +2412,14 @@
       </c>
       <c r="D44" s="18">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="E44" s="18">
         <v>45956</v>
       </c>
       <c r="F44" s="17">
         <f t="shared" ca="1" si="9"/>
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>54</v>
@@ -2469,18 +2478,18 @@
       </c>
       <c r="E46" s="20">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F46" s="19">
         <f ca="1">E46-D46</f>
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>69</v>
       </c>
       <c r="H46" s="54">
         <f ca="1">F46*2</f>
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="I46" s="19">
         <v>1</v>
@@ -2504,18 +2513,18 @@
       </c>
       <c r="E47" s="20">
         <f t="shared" ref="E47:E48" ca="1" si="10">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F47" s="19">
         <f t="shared" ref="F47:F48" ca="1" si="11">E47-D47</f>
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>69</v>
       </c>
       <c r="H47" s="54">
         <f t="shared" ref="H47:H48" ca="1" si="12">F47*2</f>
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="I47" s="19">
         <v>1</v>
@@ -2539,18 +2548,18 @@
       </c>
       <c r="E48" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F48" s="19">
         <f t="shared" ca="1" si="11"/>
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>69</v>
       </c>
       <c r="H48" s="54">
         <f t="shared" ca="1" si="12"/>
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="I48" s="19">
         <v>1</v>
@@ -2622,14 +2631,14 @@
       </c>
       <c r="D51" s="18">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="E51" s="18">
         <v>46027</v>
       </c>
       <c r="F51" s="17">
         <f ca="1">D51-E51</f>
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>54</v>
@@ -2787,7 +2796,7 @@
       <c r="B1" s="46"/>
       <c r="C1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="E1" s="46"/>
       <c r="F1" s="46"/>
@@ -2849,14 +2858,14 @@
       </c>
       <c r="E3" s="65">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F3" s="65">
         <v>45947</v>
       </c>
       <c r="G3" s="64">
         <f t="shared" ref="G3:G8" ca="1" si="0">E3-F3</f>
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H3" s="64" t="s">
         <v>54</v>
@@ -2887,14 +2896,14 @@
       </c>
       <c r="E4" s="65">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F4" s="65">
         <v>45953</v>
       </c>
       <c r="G4" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="H4" s="64" t="s">
         <v>54</v>
@@ -2925,14 +2934,14 @@
       </c>
       <c r="E5" s="65">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F5" s="65">
         <v>45956</v>
       </c>
       <c r="G5" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H5" s="64" t="s">
         <v>54</v>
@@ -2964,14 +2973,14 @@
       </c>
       <c r="E6" s="68">
         <f t="shared" ref="E6:E14" ca="1" si="2">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F6" s="68">
         <v>45910</v>
       </c>
       <c r="G6" s="67">
         <f t="shared" ca="1" si="0"/>
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="H6" s="67" t="s">
         <v>54</v>
@@ -3003,14 +3012,14 @@
       </c>
       <c r="E7" s="65">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F7" s="65">
         <v>46027</v>
       </c>
       <c r="G7" s="64">
         <f t="shared" ca="1" si="0"/>
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H7" s="64" t="s">
         <v>54</v>
@@ -3041,14 +3050,14 @@
       </c>
       <c r="E8" s="72">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F8" s="72">
         <v>46036</v>
       </c>
       <c r="G8" s="71">
         <f t="shared" ca="1" si="0"/>
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H8" s="71" t="s">
         <v>54</v>
@@ -3079,14 +3088,14 @@
       </c>
       <c r="E9" s="72">
         <f t="shared" ca="1" si="2"/>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F9" s="72">
         <v>46082</v>
       </c>
       <c r="G9" s="71">
         <f ca="1">E9-F9</f>
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="H9" s="71" t="s">
         <v>54</v>
@@ -3117,14 +3126,14 @@
       </c>
       <c r="E10" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F10" s="18">
         <v>46089</v>
       </c>
       <c r="G10" s="17">
         <f t="shared" ref="G10:G17" ca="1" si="3">E10-F10</f>
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>54</v>
@@ -3155,14 +3164,14 @@
       </c>
       <c r="E11" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F11" s="70">
         <v>46129</v>
       </c>
       <c r="G11" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>54</v>
@@ -3190,14 +3199,14 @@
       </c>
       <c r="E12" s="18">
         <f t="shared" ca="1" si="2"/>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F12" s="70">
         <v>46129</v>
       </c>
       <c r="G12" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H12" s="17" t="s">
         <v>54</v>
@@ -3225,14 +3234,14 @@
       </c>
       <c r="E13" s="72">
         <f t="shared" ca="1" si="2"/>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F13" s="72">
         <v>46182</v>
       </c>
       <c r="G13" s="71">
         <f t="shared" ca="1" si="3"/>
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H13" s="71" t="s">
         <v>54</v>
@@ -3260,14 +3269,14 @@
       </c>
       <c r="E14" s="72">
         <f t="shared" ca="1" si="2"/>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F14" s="72">
         <v>46184</v>
       </c>
       <c r="G14" s="71">
         <f t="shared" ca="1" si="3"/>
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H14" s="71" t="s">
         <v>54</v>
@@ -3295,14 +3304,14 @@
       </c>
       <c r="E15" s="18">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F15" s="18">
         <v>46216</v>
       </c>
       <c r="G15" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H15" s="69" t="s">
         <v>54</v>
@@ -3330,11 +3339,11 @@
       </c>
       <c r="E16" s="72">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F16" s="72">
         <f t="shared" ref="F16" ca="1" si="4">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="G16" s="71">
         <f t="shared" ca="1" si="3"/>
@@ -3366,14 +3375,14 @@
       </c>
       <c r="E17" s="18">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F17" s="18">
         <v>46271</v>
       </c>
       <c r="G17" s="17">
         <f t="shared" ca="1" si="3"/>
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H17" s="69" t="s">
         <v>54</v>
@@ -3450,7 +3459,7 @@
       </c>
       <c r="E21" s="93">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F21" s="93">
         <v>46311</v>
@@ -3487,7 +3496,7 @@
       </c>
       <c r="E22" s="93">
         <f t="shared" ref="E22:E23" ca="1" si="6">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F22" s="93">
         <v>46322</v>
@@ -3524,7 +3533,7 @@
       </c>
       <c r="E23" s="93">
         <f t="shared" ca="1" si="6"/>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F23" s="93">
         <v>46322</v>
@@ -3579,7 +3588,7 @@
       </c>
       <c r="B1" s="46">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="D1" s="46"/>
       <c r="E1" s="46"/>
@@ -4105,7 +4114,7 @@
       </c>
       <c r="E22" s="79">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46325</v>
       </c>
       <c r="F22" s="77" t="e">
         <f t="shared" ca="1" si="0"/>
@@ -4206,35 +4215,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" s="78" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="78" t="s">
+    <row r="27" spans="1:10" s="97" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="97" t="s">
         <v>75</v>
       </c>
-      <c r="B27" s="78" t="s">
+      <c r="B27" s="97" t="s">
         <v>76</v>
       </c>
-      <c r="C27" s="78" t="s">
+      <c r="C27" s="97" t="s">
         <v>29</v>
       </c>
-      <c r="D27" s="80">
+      <c r="D27" s="98">
         <v>46316</v>
       </c>
-      <c r="E27" s="80">
+      <c r="E27" s="98">
         <v>46337</v>
       </c>
-      <c r="F27" s="78">
+      <c r="F27" s="97">
         <f>E27-D27</f>
         <v>21</v>
       </c>
-      <c r="G27" s="78">
+      <c r="G27" s="97">
         <v>12</v>
       </c>
-      <c r="H27" s="89">
+      <c r="H27" s="99">
         <f>I27/G27</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="78" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="78" t="s">
+        <v>7</v>
+      </c>
       <c r="B28" s="78" t="s">
         <v>8</v>
       </c>
@@ -4259,36 +4271,72 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" s="78" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="78" t="s">
+    <row r="29" spans="1:10" s="97" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="97" t="s">
         <v>6</v>
       </c>
-      <c r="B29" s="78" t="s">
+      <c r="B29" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="C29" s="78" t="s">
+      <c r="C29" s="97" t="s">
         <v>29</v>
       </c>
-      <c r="D29" s="80"/>
-      <c r="E29" s="80"/>
-      <c r="H29" s="89" t="e">
-        <f t="shared" ref="H29" si="2">I29/G29</f>
+      <c r="D29" s="98" t="s">
+        <v>93</v>
+      </c>
+      <c r="E29" s="98" t="s">
+        <v>93</v>
+      </c>
+      <c r="F29" s="97" t="e">
+        <f t="shared" ref="F29:F32" si="2">E29-D29</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H29" s="99" t="e">
+        <f t="shared" ref="H29" si="3">I29/G29</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="78" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D30" s="80"/>
-      <c r="E30" s="80"/>
+      <c r="A30" s="78" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" s="78" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="78" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="80">
+        <v>46324</v>
+      </c>
+      <c r="E30" s="80">
+        <v>46345</v>
+      </c>
+      <c r="F30" s="78">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="G30" s="78">
+        <v>10</v>
+      </c>
       <c r="H30" s="89"/>
     </row>
     <row r="31" spans="1:10" s="78" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D31" s="80"/>
       <c r="E31" s="80"/>
+      <c r="F31" s="78">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="H31" s="89"/>
     </row>
     <row r="32" spans="1:10" s="78" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D32" s="80"/>
       <c r="E32" s="80"/>
+      <c r="F32" s="78">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="H32" s="89"/>
     </row>
     <row r="33" spans="1:9" s="30" customFormat="1" x14ac:dyDescent="0.25">
